--- a/research/traditional_assets/database/data/sweden/sweden_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_retail_automotive.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07657563096360194</v>
+        <v>0.07645361516381692</v>
       </c>
       <c r="C2">
-        <v>1588.486708061137</v>
+        <v>1575.611842818813</v>
       </c>
       <c r="D2">
-        <v>1526.486708061137</v>
+        <v>1532.562842818813</v>
       </c>
       <c r="E2">
-        <v>-886</v>
+        <v>-867.049</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.951</v>
       </c>
       <c r="G2">
         <v>62</v>
@@ -1585,28 +1585,28 @@
         <v>176.225</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9532353</v>
       </c>
       <c r="N2">
-        <v>176.225</v>
+        <v>175.2717647</v>
       </c>
       <c r="O2">
-        <v>36.30235</v>
+        <v>36.10598352820001</v>
       </c>
       <c r="P2">
-        <v>139.92265</v>
+        <v>139.1657811718</v>
       </c>
       <c r="Q2">
-        <v>221.82265</v>
+        <v>221.0657811718</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07657563096360194</v>
+        <v>0.07682245774122921</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307606</v>
+        <v>0.7164539894048316</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>184.8704092263474</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07645361516381692</v>
+        <v>0.07633159936403189</v>
       </c>
       <c r="C3">
-        <v>1575.611842818813</v>
+        <v>1562.785542634167</v>
       </c>
       <c r="D3">
-        <v>1532.562842818813</v>
+        <v>1538.687542634167</v>
       </c>
       <c r="E3">
-        <v>-867.049</v>
+        <v>-848.098</v>
       </c>
       <c r="F3">
-        <v>18.951</v>
+        <v>37.902</v>
       </c>
       <c r="G3">
         <v>62</v>
@@ -1667,28 +1667,28 @@
         <v>176.225</v>
       </c>
       <c r="M3">
-        <v>0.9532353</v>
+        <v>1.9064706</v>
       </c>
       <c r="N3">
-        <v>175.2717647</v>
+        <v>174.3185294</v>
       </c>
       <c r="O3">
-        <v>36.10598352820001</v>
+        <v>35.9096170564</v>
       </c>
       <c r="P3">
-        <v>139.1657811718</v>
+        <v>138.4089123436</v>
       </c>
       <c r="Q3">
-        <v>221.0657811718</v>
+        <v>220.3089123436</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07682245774122921</v>
+        <v>0.07707432180003254</v>
       </c>
       <c r="T3">
-        <v>0.7164539894048316</v>
+        <v>0.7222707113171488</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>184.8704092263474</v>
+        <v>92.43520461317368</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07633159936403189</v>
+        <v>0.07620958356424688</v>
       </c>
       <c r="C4">
-        <v>1562.785542634167</v>
+        <v>1550.008392096363</v>
       </c>
       <c r="D4">
-        <v>1538.687542634167</v>
+        <v>1544.861392096363</v>
       </c>
       <c r="E4">
-        <v>-848.098</v>
+        <v>-829.147</v>
       </c>
       <c r="F4">
-        <v>37.902</v>
+        <v>56.85299999999999</v>
       </c>
       <c r="G4">
         <v>62</v>
@@ -1749,28 +1749,28 @@
         <v>176.225</v>
       </c>
       <c r="M4">
-        <v>1.9064706</v>
+        <v>2.859705899999999</v>
       </c>
       <c r="N4">
-        <v>174.3185294</v>
+        <v>173.3652941</v>
       </c>
       <c r="O4">
-        <v>35.9096170564</v>
+        <v>35.7132505846</v>
       </c>
       <c r="P4">
-        <v>138.4089123436</v>
+        <v>137.6520435154</v>
       </c>
       <c r="Q4">
-        <v>220.3089123436</v>
+        <v>219.5520435154</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07707432180003254</v>
+        <v>0.07733137893221328</v>
       </c>
       <c r="T4">
-        <v>0.7222707113171488</v>
+        <v>0.7282073656400294</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.43520461317368</v>
+        <v>61.6234697421158</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07620958356424688</v>
+        <v>0.07608756776446186</v>
       </c>
       <c r="C5">
-        <v>1550.008392096363</v>
+        <v>1537.280985214818</v>
       </c>
       <c r="D5">
-        <v>1544.861392096363</v>
+        <v>1551.084985214818</v>
       </c>
       <c r="E5">
-        <v>-829.147</v>
+        <v>-810.196</v>
       </c>
       <c r="F5">
-        <v>56.85299999999999</v>
+        <v>75.804</v>
       </c>
       <c r="G5">
         <v>62</v>
@@ -1831,28 +1831,28 @@
         <v>176.225</v>
       </c>
       <c r="M5">
-        <v>2.859705899999999</v>
+        <v>3.8129412</v>
       </c>
       <c r="N5">
-        <v>173.3652941</v>
+        <v>172.4120588</v>
       </c>
       <c r="O5">
-        <v>35.7132505846</v>
+        <v>35.5168841128</v>
       </c>
       <c r="P5">
-        <v>137.6520435154</v>
+        <v>136.8951746872</v>
       </c>
       <c r="Q5">
-        <v>219.5520435154</v>
+        <v>218.7951746872</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07733137893221328</v>
+        <v>0.07759379142131444</v>
       </c>
       <c r="T5">
-        <v>0.7282073656400294</v>
+        <v>0.7342677002613033</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.6234697421158</v>
+        <v>46.21760230658683</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07608756776446186</v>
+        <v>0.07596555196467684</v>
       </c>
       <c r="C6">
-        <v>1537.280985214818</v>
+        <v>1524.603925609714</v>
       </c>
       <c r="D6">
-        <v>1551.084985214818</v>
+        <v>1557.358925609714</v>
       </c>
       <c r="E6">
-        <v>-810.196</v>
+        <v>-791.245</v>
       </c>
       <c r="F6">
-        <v>75.804</v>
+        <v>94.755</v>
       </c>
       <c r="G6">
         <v>62</v>
@@ -1913,28 +1913,28 @@
         <v>176.225</v>
       </c>
       <c r="M6">
-        <v>3.8129412</v>
+        <v>4.766176499999999</v>
       </c>
       <c r="N6">
-        <v>172.4120588</v>
+        <v>171.4588235</v>
       </c>
       <c r="O6">
-        <v>35.5168841128</v>
+        <v>35.320517641</v>
       </c>
       <c r="P6">
-        <v>136.8951746872</v>
+        <v>136.138305859</v>
       </c>
       <c r="Q6">
-        <v>218.7951746872</v>
+        <v>218.038305859</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07759379142131444</v>
+        <v>0.07786172838387036</v>
       </c>
       <c r="T6">
-        <v>0.7342677002613033</v>
+        <v>0.740455620874604</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.21760230658683</v>
+        <v>36.97408184526947</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07596555196467684</v>
+        <v>0.07584353616489181</v>
       </c>
       <c r="C7">
-        <v>1524.603925609714</v>
+        <v>1511.977826707165</v>
       </c>
       <c r="D7">
-        <v>1557.358925609714</v>
+        <v>1563.683826707165</v>
       </c>
       <c r="E7">
-        <v>-791.245</v>
+        <v>-772.294</v>
       </c>
       <c r="F7">
-        <v>94.755</v>
+        <v>113.706</v>
       </c>
       <c r="G7">
         <v>62</v>
@@ -1995,28 +1995,28 @@
         <v>176.225</v>
       </c>
       <c r="M7">
-        <v>4.766176499999999</v>
+        <v>5.7194118</v>
       </c>
       <c r="N7">
-        <v>171.4588235</v>
+        <v>170.5055882</v>
       </c>
       <c r="O7">
-        <v>35.320517641</v>
+        <v>35.1241511692</v>
       </c>
       <c r="P7">
-        <v>136.138305859</v>
+        <v>135.3814370308</v>
       </c>
       <c r="Q7">
-        <v>218.038305859</v>
+        <v>217.2814370308</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07786172838387036</v>
+        <v>0.07813536613286363</v>
       </c>
       <c r="T7">
-        <v>0.740455620874604</v>
+        <v>0.7467751993732941</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.97408184526947</v>
+        <v>30.8117348710579</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07584353616489181</v>
+        <v>0.07572152036510681</v>
       </c>
       <c r="C8">
-        <v>1511.977826707165</v>
+        <v>1499.403311939147</v>
       </c>
       <c r="D8">
-        <v>1563.683826707165</v>
+        <v>1570.060311939147</v>
       </c>
       <c r="E8">
-        <v>-772.294</v>
+        <v>-753.3430000000001</v>
       </c>
       <c r="F8">
-        <v>113.706</v>
+        <v>132.657</v>
       </c>
       <c r="G8">
         <v>62</v>
@@ -2077,28 +2077,28 @@
         <v>176.225</v>
       </c>
       <c r="M8">
-        <v>5.719411799999999</v>
+        <v>6.672647099999999</v>
       </c>
       <c r="N8">
-        <v>170.5055882</v>
+        <v>169.5523529</v>
       </c>
       <c r="O8">
-        <v>35.1241511692</v>
+        <v>34.9277846974</v>
       </c>
       <c r="P8">
-        <v>135.3814370308</v>
+        <v>134.6245682026</v>
       </c>
       <c r="Q8">
-        <v>217.2814370308</v>
+        <v>216.5245682026</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07813536613286363</v>
+        <v>0.07841488856463097</v>
       </c>
       <c r="T8">
-        <v>0.7467751993732941</v>
+        <v>0.7532306827859344</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.8117348710579</v>
+        <v>26.41005846090677</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07572152036510679</v>
+        <v>0.07559950456532177</v>
       </c>
       <c r="C9">
-        <v>1499.403311939148</v>
+        <v>1486.881014948355</v>
       </c>
       <c r="D9">
-        <v>1570.060311939148</v>
+        <v>1576.489014948355</v>
       </c>
       <c r="E9">
-        <v>-753.343</v>
+        <v>-734.3920000000001</v>
       </c>
       <c r="F9">
-        <v>132.657</v>
+        <v>151.608</v>
       </c>
       <c r="G9">
         <v>62</v>
@@ -2159,28 +2159,28 @@
         <v>176.225</v>
       </c>
       <c r="M9">
-        <v>6.6726471</v>
+        <v>7.6258824</v>
       </c>
       <c r="N9">
-        <v>169.5523529</v>
+        <v>168.5991176</v>
       </c>
       <c r="O9">
-        <v>34.9277846974</v>
+        <v>34.7314182256</v>
       </c>
       <c r="P9">
-        <v>134.6245682026</v>
+        <v>133.8676993744</v>
       </c>
       <c r="Q9">
-        <v>216.5245682026</v>
+        <v>215.7676993744</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07841488856463097</v>
+        <v>0.07870048757100193</v>
       </c>
       <c r="T9">
-        <v>0.7532306827859344</v>
+        <v>0.7598265027945018</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.41005846090676</v>
+        <v>23.10880115329342</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07559950456532177</v>
+        <v>0.07547748876553677</v>
       </c>
       <c r="C10">
-        <v>1486.881014948355</v>
+        <v>1474.411579798093</v>
       </c>
       <c r="D10">
-        <v>1576.489014948355</v>
+        <v>1582.970579798093</v>
       </c>
       <c r="E10">
-        <v>-734.3920000000001</v>
+        <v>-715.441</v>
       </c>
       <c r="F10">
-        <v>151.608</v>
+        <v>170.559</v>
       </c>
       <c r="G10">
         <v>62</v>
@@ -2241,28 +2241,28 @@
         <v>176.225</v>
       </c>
       <c r="M10">
-        <v>7.6258824</v>
+        <v>8.579117699999999</v>
       </c>
       <c r="N10">
-        <v>168.5991176</v>
+        <v>167.6458823</v>
       </c>
       <c r="O10">
-        <v>34.7314182256</v>
+        <v>34.5350517538</v>
       </c>
       <c r="P10">
-        <v>133.8676993744</v>
+        <v>133.1108305462</v>
       </c>
       <c r="Q10">
-        <v>215.7676993744</v>
+        <v>215.0108305462</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07870048757100193</v>
+        <v>0.07899236347861183</v>
       </c>
       <c r="T10">
-        <v>0.7598265027945018</v>
+        <v>0.7665672858801805</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.10880115329342</v>
+        <v>20.54115658070526</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07547748876553677</v>
+        <v>0.07535547296575174</v>
       </c>
       <c r="C11">
-        <v>1474.411579798093</v>
+        <v>1461.995661187386</v>
       </c>
       <c r="D11">
-        <v>1582.970579798093</v>
+        <v>1589.505661187386</v>
       </c>
       <c r="E11">
-        <v>-715.441</v>
+        <v>-696.49</v>
       </c>
       <c r="F11">
-        <v>170.559</v>
+        <v>189.51</v>
       </c>
       <c r="G11">
         <v>62</v>
@@ -2323,28 +2323,28 @@
         <v>176.225</v>
       </c>
       <c r="M11">
-        <v>8.579117699999999</v>
+        <v>9.532352999999997</v>
       </c>
       <c r="N11">
-        <v>167.6458823</v>
+        <v>166.692647</v>
       </c>
       <c r="O11">
-        <v>34.5350517538</v>
+        <v>34.338685282</v>
       </c>
       <c r="P11">
-        <v>133.1108305462</v>
+        <v>132.353961718</v>
       </c>
       <c r="Q11">
-        <v>215.0108305462</v>
+        <v>214.253961718</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07899236347861183</v>
+        <v>0.07929072551750194</v>
       </c>
       <c r="T11">
-        <v>0.7665672858801805</v>
+        <v>0.7734578641455411</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.54115658070526</v>
+        <v>18.48704092263474</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07535547296575174</v>
+        <v>0.07523345716596672</v>
       </c>
       <c r="C12">
-        <v>1461.995661187386</v>
+        <v>1449.633924671421</v>
       </c>
       <c r="D12">
-        <v>1589.505661187386</v>
+        <v>1596.094924671421</v>
       </c>
       <c r="E12">
-        <v>-696.49</v>
+        <v>-677.539</v>
       </c>
       <c r="F12">
-        <v>189.51</v>
+        <v>208.461</v>
       </c>
       <c r="G12">
         <v>62</v>
@@ -2405,28 +2405,28 @@
         <v>176.225</v>
       </c>
       <c r="M12">
-        <v>9.532352999999999</v>
+        <v>10.4855883</v>
       </c>
       <c r="N12">
-        <v>166.692647</v>
+        <v>165.7394117</v>
       </c>
       <c r="O12">
-        <v>34.338685282</v>
+        <v>34.1423188102</v>
       </c>
       <c r="P12">
-        <v>132.353961718</v>
+        <v>131.5970928898</v>
       </c>
       <c r="Q12">
-        <v>214.253961718</v>
+        <v>213.4970928898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07929072551750194</v>
+        <v>0.07959579232131092</v>
       </c>
       <c r="T12">
-        <v>0.7734578641455411</v>
+        <v>0.780503286866303</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.48704092263474</v>
+        <v>16.80640083875885</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07523345716596672</v>
+        <v>0.07511144136618171</v>
       </c>
       <c r="C13">
-        <v>1449.633924671421</v>
+        <v>1437.327046887507</v>
       </c>
       <c r="D13">
-        <v>1596.094924671421</v>
+        <v>1602.739046887507</v>
       </c>
       <c r="E13">
-        <v>-677.539</v>
+        <v>-658.588</v>
       </c>
       <c r="F13">
-        <v>208.461</v>
+        <v>227.412</v>
       </c>
       <c r="G13">
         <v>62</v>
@@ -2487,28 +2487,28 @@
         <v>176.225</v>
       </c>
       <c r="M13">
-        <v>10.4855883</v>
+        <v>11.4388236</v>
       </c>
       <c r="N13">
-        <v>165.7394117</v>
+        <v>164.7861764</v>
       </c>
       <c r="O13">
-        <v>34.1423188102</v>
+        <v>33.9459523384</v>
       </c>
       <c r="P13">
-        <v>131.5970928898</v>
+        <v>130.8402240616</v>
       </c>
       <c r="Q13">
-        <v>213.4970928898</v>
+        <v>212.7402240616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07959579232131092</v>
+        <v>0.07990779246157012</v>
       </c>
       <c r="T13">
-        <v>0.780503286866303</v>
+        <v>0.7877088328307185</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.80640083875885</v>
+        <v>15.40586743552895</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07511144136618171</v>
+        <v>0.07498942556639668</v>
       </c>
       <c r="C14">
-        <v>1437.327046887507</v>
+        <v>1425.075715786706</v>
       </c>
       <c r="D14">
-        <v>1602.739046887507</v>
+        <v>1609.438715786707</v>
       </c>
       <c r="E14">
-        <v>-658.588</v>
+        <v>-639.6369999999999</v>
       </c>
       <c r="F14">
-        <v>227.412</v>
+        <v>246.363</v>
       </c>
       <c r="G14">
         <v>62</v>
@@ -2569,28 +2569,28 @@
         <v>176.225</v>
       </c>
       <c r="M14">
-        <v>11.4388236</v>
+        <v>12.3920589</v>
       </c>
       <c r="N14">
-        <v>164.7861764</v>
+        <v>163.8329411</v>
       </c>
       <c r="O14">
-        <v>33.9459523384</v>
+        <v>33.7495858666</v>
       </c>
       <c r="P14">
-        <v>130.8402240616</v>
+        <v>130.0833552334</v>
       </c>
       <c r="Q14">
-        <v>212.7402240616</v>
+        <v>211.9833552334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07990779246157012</v>
+        <v>0.08022696501884675</v>
       </c>
       <c r="T14">
-        <v>0.7877088328307185</v>
+        <v>0.7950800235299481</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.40586743552895</v>
+        <v>14.22080070971903</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07498942556639668</v>
+        <v>0.07486740976661166</v>
       </c>
       <c r="C15">
-        <v>1425.075715786706</v>
+        <v>1412.880630871278</v>
       </c>
       <c r="D15">
-        <v>1609.438715786707</v>
+        <v>1616.194630871278</v>
       </c>
       <c r="E15">
-        <v>-639.6369999999999</v>
+        <v>-620.6859999999999</v>
       </c>
       <c r="F15">
-        <v>246.363</v>
+        <v>265.314</v>
       </c>
       <c r="G15">
         <v>62</v>
@@ -2651,28 +2651,28 @@
         <v>176.225</v>
       </c>
       <c r="M15">
-        <v>12.3920589</v>
+        <v>13.3452942</v>
       </c>
       <c r="N15">
-        <v>163.8329411</v>
+        <v>162.8797058</v>
       </c>
       <c r="O15">
-        <v>33.7495858666</v>
+        <v>33.5532193948</v>
       </c>
       <c r="P15">
-        <v>130.0833552334</v>
+        <v>129.3264864052</v>
       </c>
       <c r="Q15">
-        <v>211.9833552334</v>
+        <v>211.2264864052</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08022696501884675</v>
+        <v>0.0805535601937345</v>
       </c>
       <c r="T15">
-        <v>0.7950800235299481</v>
+        <v>0.8026226372686948</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.22080070971903</v>
+        <v>13.20502923045338</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07486740976661166</v>
+        <v>0.07492404396682664</v>
       </c>
       <c r="C16">
-        <v>1412.880630871278</v>
+        <v>1390.786801859779</v>
       </c>
       <c r="D16">
-        <v>1616.194630871278</v>
+        <v>1613.051801859779</v>
       </c>
       <c r="E16">
-        <v>-620.6859999999999</v>
+        <v>-601.7349999999999</v>
       </c>
       <c r="F16">
-        <v>265.314</v>
+        <v>284.265</v>
       </c>
       <c r="G16">
         <v>62</v>
@@ -2733,45 +2733,45 @@
         <v>176.225</v>
       </c>
       <c r="M16">
-        <v>13.3452942</v>
+        <v>14.724927</v>
       </c>
       <c r="N16">
-        <v>162.8797058</v>
+        <v>161.500073</v>
       </c>
       <c r="O16">
-        <v>33.5532193948</v>
+        <v>33.269015038</v>
       </c>
       <c r="P16">
-        <v>129.3264864052</v>
+        <v>128.231057962</v>
       </c>
       <c r="Q16">
-        <v>211.2264864052</v>
+        <v>210.131057962</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0805535601937345</v>
+        <v>0.08088783996097251</v>
       </c>
       <c r="T16">
-        <v>0.8026226372686948</v>
+        <v>0.8103427242718825</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.20502923045338</v>
+        <v>11.96780126651901</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07492404396682664</v>
+        <v>0.07481393816704161</v>
       </c>
       <c r="C17">
-        <v>1390.786801859779</v>
+        <v>1377.957216943657</v>
       </c>
       <c r="D17">
-        <v>1613.051801859779</v>
+        <v>1619.173216943657</v>
       </c>
       <c r="E17">
-        <v>-601.735</v>
+        <v>-582.784</v>
       </c>
       <c r="F17">
-        <v>284.265</v>
+        <v>303.216</v>
       </c>
       <c r="G17">
         <v>62</v>
@@ -2815,28 +2815,28 @@
         <v>176.225</v>
       </c>
       <c r="M17">
-        <v>14.724927</v>
+        <v>15.7065888</v>
       </c>
       <c r="N17">
-        <v>161.500073</v>
+        <v>160.5184112</v>
       </c>
       <c r="O17">
-        <v>33.269015038</v>
+        <v>33.0667927072</v>
       </c>
       <c r="P17">
-        <v>128.231057962</v>
+        <v>127.4516184928</v>
       </c>
       <c r="Q17">
-        <v>210.131057962</v>
+        <v>209.3516184928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08088783996097251</v>
+        <v>0.08123007877028765</v>
       </c>
       <c r="T17">
-        <v>0.8103427242718825</v>
+        <v>0.8182466228703842</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.96780126651901</v>
+        <v>11.21981368736157</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07481393816704161</v>
+        <v>0.0747038323672566</v>
       </c>
       <c r="C18">
-        <v>1377.957216943657</v>
+        <v>1365.174269670258</v>
       </c>
       <c r="D18">
-        <v>1619.173216943657</v>
+        <v>1625.341269670258</v>
       </c>
       <c r="E18">
-        <v>-582.784</v>
+        <v>-563.833</v>
       </c>
       <c r="F18">
-        <v>303.216</v>
+        <v>322.167</v>
       </c>
       <c r="G18">
         <v>62</v>
@@ -2897,28 +2897,28 @@
         <v>176.225</v>
       </c>
       <c r="M18">
-        <v>15.7065888</v>
+        <v>16.6882506</v>
       </c>
       <c r="N18">
-        <v>160.5184112</v>
+        <v>159.5367494</v>
       </c>
       <c r="O18">
-        <v>33.0667927072</v>
+        <v>32.8645703764</v>
       </c>
       <c r="P18">
-        <v>127.4516184928</v>
+        <v>126.6721790236</v>
       </c>
       <c r="Q18">
-        <v>209.3516184928</v>
+        <v>208.5721790236</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08123007877028765</v>
+        <v>0.08158056429789952</v>
       </c>
       <c r="T18">
-        <v>0.8182466228703842</v>
+        <v>0.8263409768568016</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.21981368736157</v>
+        <v>10.55982464692854</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0747038323672566</v>
+        <v>0.07459372656747157</v>
       </c>
       <c r="C19">
-        <v>1365.174269670258</v>
+        <v>1352.438495059764</v>
       </c>
       <c r="D19">
-        <v>1625.341269670258</v>
+        <v>1631.556495059764</v>
       </c>
       <c r="E19">
-        <v>-563.833</v>
+        <v>-544.8819999999999</v>
       </c>
       <c r="F19">
-        <v>322.167</v>
+        <v>341.1180000000001</v>
       </c>
       <c r="G19">
         <v>62</v>
@@ -2979,28 +2979,28 @@
         <v>176.225</v>
       </c>
       <c r="M19">
-        <v>16.6882506</v>
+        <v>17.6699124</v>
       </c>
       <c r="N19">
-        <v>159.5367494</v>
+        <v>158.5550876</v>
       </c>
       <c r="O19">
-        <v>32.8645703764</v>
+        <v>32.6623480456</v>
       </c>
       <c r="P19">
-        <v>126.6721790236</v>
+        <v>125.8927395544</v>
       </c>
       <c r="Q19">
-        <v>208.5721790236</v>
+        <v>207.7927395544</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08158056429789952</v>
+        <v>0.08193959825301411</v>
       </c>
       <c r="T19">
-        <v>0.8263409768568016</v>
+        <v>0.8346327541111805</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.55982464692854</v>
+        <v>9.973167722099175</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07459372656747157</v>
+        <v>0.07474008276768657</v>
       </c>
       <c r="C20">
-        <v>1352.438495059764</v>
+        <v>1325.236364233018</v>
       </c>
       <c r="D20">
-        <v>1631.556495059764</v>
+        <v>1623.305364233018</v>
       </c>
       <c r="E20">
-        <v>-544.8820000000001</v>
+        <v>-525.931</v>
       </c>
       <c r="F20">
-        <v>341.118</v>
+        <v>360.069</v>
       </c>
       <c r="G20">
         <v>62</v>
@@ -3061,45 +3061,45 @@
         <v>176.225</v>
       </c>
       <c r="M20">
-        <v>17.6699124</v>
+        <v>19.2636915</v>
       </c>
       <c r="N20">
-        <v>158.5550876</v>
+        <v>156.9613085</v>
       </c>
       <c r="O20">
-        <v>32.66234804560001</v>
+        <v>32.334029551</v>
       </c>
       <c r="P20">
-        <v>125.8927395544</v>
+        <v>124.627278949</v>
       </c>
       <c r="Q20">
-        <v>207.7927395544</v>
+        <v>206.527278949</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08193959825301411</v>
+        <v>0.08230749724405748</v>
       </c>
       <c r="T20">
-        <v>0.8346327541111805</v>
+        <v>0.8431292666064083</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.973167722099179</v>
+        <v>9.148038941549704</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07474008276768657</v>
+        <v>0.07464347496790155</v>
       </c>
       <c r="C21">
-        <v>1325.236364233018</v>
+        <v>1311.722433094945</v>
       </c>
       <c r="D21">
-        <v>1623.305364233018</v>
+        <v>1628.742433094945</v>
       </c>
       <c r="E21">
-        <v>-525.931</v>
+        <v>-506.98</v>
       </c>
       <c r="F21">
-        <v>360.069</v>
+        <v>379.02</v>
       </c>
       <c r="G21">
         <v>62</v>
@@ -3143,28 +3143,28 @@
         <v>176.225</v>
       </c>
       <c r="M21">
-        <v>19.2636915</v>
+        <v>20.27757</v>
       </c>
       <c r="N21">
-        <v>156.9613085</v>
+        <v>155.94743</v>
       </c>
       <c r="O21">
-        <v>32.334029551</v>
+        <v>32.12517058</v>
       </c>
       <c r="P21">
-        <v>124.627278949</v>
+        <v>123.82225942</v>
       </c>
       <c r="Q21">
-        <v>206.527278949</v>
+        <v>205.72225942</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08230749724405748</v>
+        <v>0.08268459370987694</v>
       </c>
       <c r="T21">
-        <v>0.8431292666064083</v>
+        <v>0.8518381919140168</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.148038941549704</v>
+        <v>8.690636994472218</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07464347496790155</v>
+        <v>0.07454686716811654</v>
       </c>
       <c r="C22">
-        <v>1311.722433094945</v>
+        <v>1298.245045991878</v>
       </c>
       <c r="D22">
-        <v>1628.742433094945</v>
+        <v>1634.216045991878</v>
       </c>
       <c r="E22">
-        <v>-506.98</v>
+        <v>-488.029</v>
       </c>
       <c r="F22">
-        <v>379.02</v>
+        <v>397.971</v>
       </c>
       <c r="G22">
         <v>62</v>
@@ -3225,28 +3225,28 @@
         <v>176.225</v>
       </c>
       <c r="M22">
-        <v>20.27757</v>
+        <v>21.2914485</v>
       </c>
       <c r="N22">
-        <v>155.94743</v>
+        <v>154.9335515</v>
       </c>
       <c r="O22">
-        <v>32.12517058</v>
+        <v>31.916311609</v>
       </c>
       <c r="P22">
-        <v>123.82225942</v>
+        <v>123.017239891</v>
       </c>
       <c r="Q22">
-        <v>205.72225942</v>
+        <v>204.917239891</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08268459370987694</v>
+        <v>0.08307123692166649</v>
       </c>
       <c r="T22">
-        <v>0.8518381919140168</v>
+        <v>0.8607675963433367</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.690636994472218</v>
+        <v>8.276797137592588</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07454686716811654</v>
+        <v>0.0744502593683315</v>
       </c>
       <c r="C23">
-        <v>1298.245045991878</v>
+        <v>1284.804572599926</v>
       </c>
       <c r="D23">
-        <v>1634.216045991878</v>
+        <v>1639.726572599926</v>
       </c>
       <c r="E23">
-        <v>-488.0290000000001</v>
+        <v>-469.078</v>
       </c>
       <c r="F23">
-        <v>397.9709999999999</v>
+        <v>416.922</v>
       </c>
       <c r="G23">
         <v>62</v>
@@ -3307,28 +3307,28 @@
         <v>176.225</v>
       </c>
       <c r="M23">
-        <v>21.2914485</v>
+        <v>22.305327</v>
       </c>
       <c r="N23">
-        <v>154.9335515</v>
+        <v>153.919673</v>
       </c>
       <c r="O23">
-        <v>31.916311609</v>
+        <v>31.707452638</v>
       </c>
       <c r="P23">
-        <v>123.017239891</v>
+        <v>122.212220362</v>
       </c>
       <c r="Q23">
-        <v>204.917239891</v>
+        <v>204.112220362</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08307123692166649</v>
+        <v>0.08346779406196346</v>
       </c>
       <c r="T23">
-        <v>0.8607675963433367</v>
+        <v>0.8699259598605878</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.276797137592588</v>
+        <v>7.900579085883834</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0744502593683315</v>
+        <v>0.07449974756854649</v>
       </c>
       <c r="C24">
-        <v>1284.804572599926</v>
+        <v>1263.026122054277</v>
       </c>
       <c r="D24">
-        <v>1639.726572599926</v>
+        <v>1636.899122054277</v>
       </c>
       <c r="E24">
-        <v>-469.078</v>
+        <v>-450.127</v>
       </c>
       <c r="F24">
-        <v>416.922</v>
+        <v>435.873</v>
       </c>
       <c r="G24">
         <v>62</v>
@@ -3389,45 +3389,45 @@
         <v>176.225</v>
       </c>
       <c r="M24">
-        <v>22.305327</v>
+        <v>23.6679039</v>
       </c>
       <c r="N24">
-        <v>153.919673</v>
+        <v>152.5570961</v>
       </c>
       <c r="O24">
-        <v>31.707452638</v>
+        <v>31.4267617966</v>
       </c>
       <c r="P24">
-        <v>122.212220362</v>
+        <v>121.1303343034</v>
       </c>
       <c r="Q24">
-        <v>204.112220362</v>
+        <v>203.0303343034</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08346779406196346</v>
+        <v>0.08387465138772271</v>
       </c>
       <c r="T24">
-        <v>0.8699259598605878</v>
+        <v>0.8793222029497159</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.206</v>
       </c>
       <c r="W24">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.900579085883834</v>
+        <v>7.445737516282547</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07449974756854649</v>
+        <v>0.07440949176876147</v>
       </c>
       <c r="C25">
-        <v>1263.026122054277</v>
+        <v>1249.239129881558</v>
       </c>
       <c r="D25">
-        <v>1636.899122054277</v>
+        <v>1642.063129881558</v>
       </c>
       <c r="E25">
-        <v>-450.127</v>
+        <v>-431.176</v>
       </c>
       <c r="F25">
-        <v>435.873</v>
+        <v>454.824</v>
       </c>
       <c r="G25">
         <v>62</v>
@@ -3471,28 +3471,28 @@
         <v>176.225</v>
       </c>
       <c r="M25">
-        <v>23.6679039</v>
+        <v>24.6969432</v>
       </c>
       <c r="N25">
-        <v>152.5570961</v>
+        <v>151.5280568</v>
       </c>
       <c r="O25">
-        <v>31.4267617966</v>
+        <v>31.2147797008</v>
       </c>
       <c r="P25">
-        <v>121.1303343034</v>
+        <v>120.3132770992</v>
       </c>
       <c r="Q25">
-        <v>203.0303343034</v>
+        <v>202.2132770992</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08387465138772271</v>
+        <v>0.08429221548521246</v>
       </c>
       <c r="T25">
-        <v>0.8793222029497159</v>
+        <v>0.8889657155938209</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.445737516282547</v>
+        <v>7.135498453104107</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07440949176876147</v>
+        <v>0.07431923596897644</v>
       </c>
       <c r="C26">
-        <v>1249.239129881558</v>
+        <v>1235.484823132604</v>
       </c>
       <c r="D26">
-        <v>1642.063129881558</v>
+        <v>1647.259823132604</v>
       </c>
       <c r="E26">
-        <v>-431.176</v>
+        <v>-412.225</v>
       </c>
       <c r="F26">
-        <v>454.824</v>
+        <v>473.775</v>
       </c>
       <c r="G26">
         <v>62</v>
@@ -3553,28 +3553,28 @@
         <v>176.225</v>
       </c>
       <c r="M26">
-        <v>24.6969432</v>
+        <v>25.7259825</v>
       </c>
       <c r="N26">
-        <v>151.5280568</v>
+        <v>150.4990175</v>
       </c>
       <c r="O26">
-        <v>31.2147797008</v>
+        <v>31.002797605</v>
       </c>
       <c r="P26">
-        <v>120.3132770992</v>
+        <v>119.496219895</v>
       </c>
       <c r="Q26">
-        <v>202.2132770992</v>
+        <v>201.396219895</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08429221548521246</v>
+        <v>0.08472091462530192</v>
       </c>
       <c r="T26">
-        <v>0.8889657155938209</v>
+        <v>0.8988663885751019</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.135498453104107</v>
+        <v>6.850078514979942</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07431923596897644</v>
+        <v>0.07422898016919142</v>
       </c>
       <c r="C27">
-        <v>1235.484823132604</v>
+        <v>1221.763513114648</v>
       </c>
       <c r="D27">
-        <v>1647.259823132604</v>
+        <v>1652.489513114648</v>
       </c>
       <c r="E27">
-        <v>-412.225</v>
+        <v>-393.274</v>
       </c>
       <c r="F27">
-        <v>473.775</v>
+        <v>492.726</v>
       </c>
       <c r="G27">
         <v>62</v>
@@ -3635,28 +3635,28 @@
         <v>176.225</v>
       </c>
       <c r="M27">
-        <v>25.7259825</v>
+        <v>26.7550218</v>
       </c>
       <c r="N27">
-        <v>150.4990175</v>
+        <v>149.4699782</v>
       </c>
       <c r="O27">
-        <v>31.002797605</v>
+        <v>30.7908155092</v>
       </c>
       <c r="P27">
-        <v>119.496219895</v>
+        <v>118.6791626908</v>
       </c>
       <c r="Q27">
-        <v>201.396219895</v>
+        <v>200.5791626908</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08472091462530192</v>
+        <v>0.08516120022863705</v>
       </c>
       <c r="T27">
-        <v>0.8988663885751019</v>
+        <v>0.9090346473126339</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.850078514979942</v>
+        <v>6.586613956711482</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07422898016919142</v>
+        <v>0.0741387243694064</v>
       </c>
       <c r="C28">
-        <v>1221.763513114648</v>
+        <v>1208.075515100847</v>
       </c>
       <c r="D28">
-        <v>1652.489513114648</v>
+        <v>1657.752515100847</v>
       </c>
       <c r="E28">
-        <v>-393.274</v>
+        <v>-374.323</v>
       </c>
       <c r="F28">
-        <v>492.726</v>
+        <v>511.677</v>
       </c>
       <c r="G28">
         <v>62</v>
@@ -3717,28 +3717,28 @@
         <v>176.225</v>
       </c>
       <c r="M28">
-        <v>26.7550218</v>
+        <v>27.7840611</v>
       </c>
       <c r="N28">
-        <v>149.4699782</v>
+        <v>148.4409389</v>
       </c>
       <c r="O28">
-        <v>30.7908155092</v>
+        <v>30.5788334134</v>
       </c>
       <c r="P28">
-        <v>118.6791626908</v>
+        <v>117.8621054866</v>
       </c>
       <c r="Q28">
-        <v>200.5791626908</v>
+        <v>199.7621054866</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08516120022863705</v>
+        <v>0.08561354845124164</v>
       </c>
       <c r="T28">
-        <v>0.9090346473126339</v>
+        <v>0.9194814884813312</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.586613956711482</v>
+        <v>6.342665291648094</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0741387243694064</v>
+        <v>0.07404846856962138</v>
       </c>
       <c r="C29">
-        <v>1208.075515100847</v>
+        <v>1194.421148393632</v>
       </c>
       <c r="D29">
-        <v>1657.752515100847</v>
+        <v>1663.049148393632</v>
       </c>
       <c r="E29">
-        <v>-374.323</v>
+        <v>-355.372</v>
       </c>
       <c r="F29">
-        <v>511.677</v>
+        <v>530.628</v>
       </c>
       <c r="G29">
         <v>62</v>
@@ -3799,28 +3799,28 @@
         <v>176.225</v>
       </c>
       <c r="M29">
-        <v>27.7840611</v>
+        <v>28.8131004</v>
       </c>
       <c r="N29">
-        <v>148.4409389</v>
+        <v>147.4118996</v>
       </c>
       <c r="O29">
-        <v>30.5788334134</v>
+        <v>30.3668513176</v>
       </c>
       <c r="P29">
-        <v>117.8621054866</v>
+        <v>117.0450482824</v>
       </c>
       <c r="Q29">
-        <v>199.7621054866</v>
+        <v>198.9450482824</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08561354845124164</v>
+        <v>0.08607846190225192</v>
       </c>
       <c r="T29">
-        <v>0.9194814884813312</v>
+        <v>0.9302185196824923</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.342665291648094</v>
+        <v>6.116141531232091</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07404846856962138</v>
+        <v>0.07418847276983637</v>
       </c>
       <c r="C30">
-        <v>1194.421148393632</v>
+        <v>1167.26844385578</v>
       </c>
       <c r="D30">
-        <v>1663.049148393632</v>
+        <v>1654.84744385578</v>
       </c>
       <c r="E30">
-        <v>-355.372</v>
+        <v>-336.4209999999999</v>
       </c>
       <c r="F30">
-        <v>530.628</v>
+        <v>549.5790000000001</v>
       </c>
       <c r="G30">
         <v>62</v>
@@ -3881,45 +3881,45 @@
         <v>176.225</v>
       </c>
       <c r="M30">
-        <v>28.8131004</v>
+        <v>30.39171870000001</v>
       </c>
       <c r="N30">
-        <v>147.4118996</v>
+        <v>145.8332813</v>
       </c>
       <c r="O30">
-        <v>30.3668513176</v>
+        <v>30.0416559478</v>
       </c>
       <c r="P30">
-        <v>117.0450482824</v>
+        <v>115.7916253522</v>
       </c>
       <c r="Q30">
-        <v>198.9450482824</v>
+        <v>197.6916253522</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08607846190225192</v>
+        <v>0.08655647150681178</v>
       </c>
       <c r="T30">
-        <v>0.9302185196824923</v>
+        <v>0.9412580024667845</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.206</v>
       </c>
       <c r="W30">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.116141531232091</v>
+        <v>5.798454563874334</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07418847276983637</v>
+        <v>0.07410615697005134</v>
       </c>
       <c r="C31">
-        <v>1167.26844385578</v>
+        <v>1153.129827642365</v>
       </c>
       <c r="D31">
-        <v>1654.84744385578</v>
+        <v>1659.659827642365</v>
       </c>
       <c r="E31">
-        <v>-336.421</v>
+        <v>-317.47</v>
       </c>
       <c r="F31">
-        <v>549.579</v>
+        <v>568.53</v>
       </c>
       <c r="G31">
         <v>62</v>
@@ -3963,28 +3963,28 @@
         <v>176.225</v>
       </c>
       <c r="M31">
-        <v>30.3917187</v>
+        <v>31.439709</v>
       </c>
       <c r="N31">
-        <v>145.8332813</v>
+        <v>144.785291</v>
       </c>
       <c r="O31">
-        <v>30.04165594780001</v>
+        <v>29.825769946</v>
       </c>
       <c r="P31">
-        <v>115.7916253522</v>
+        <v>114.959521054</v>
       </c>
       <c r="Q31">
-        <v>197.6916253522</v>
+        <v>196.859521054</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08655647150681178</v>
+        <v>0.08704813852864476</v>
       </c>
       <c r="T31">
-        <v>0.9412580024667845</v>
+        <v>0.9526128990449138</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.798454563874336</v>
+        <v>5.605172745078525</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07410615697005134</v>
+        <v>0.07402384117026632</v>
       </c>
       <c r="C32">
-        <v>1153.129827642365</v>
+        <v>1139.019282393342</v>
       </c>
       <c r="D32">
-        <v>1659.659827642365</v>
+        <v>1664.500282393342</v>
       </c>
       <c r="E32">
-        <v>-317.47</v>
+        <v>-298.519</v>
       </c>
       <c r="F32">
-        <v>568.53</v>
+        <v>587.481</v>
       </c>
       <c r="G32">
         <v>62</v>
@@ -4045,28 +4045,28 @@
         <v>176.225</v>
       </c>
       <c r="M32">
-        <v>31.439709</v>
+        <v>32.4876993</v>
       </c>
       <c r="N32">
-        <v>144.785291</v>
+        <v>143.7373007</v>
       </c>
       <c r="O32">
-        <v>29.825769946</v>
+        <v>29.6098839442</v>
       </c>
       <c r="P32">
-        <v>114.959521054</v>
+        <v>114.1274167558</v>
       </c>
       <c r="Q32">
-        <v>196.859521054</v>
+        <v>196.0274167558</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08704813852864476</v>
+        <v>0.08755405676850192</v>
       </c>
       <c r="T32">
-        <v>0.9526128990449138</v>
+        <v>0.9642969230600903</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.605172745078525</v>
+        <v>5.424360721043733</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07402384117026632</v>
+        <v>0.07394152537048129</v>
       </c>
       <c r="C33">
-        <v>1139.019282393342</v>
+        <v>1124.937054436926</v>
       </c>
       <c r="D33">
-        <v>1664.500282393342</v>
+        <v>1669.369054436926</v>
       </c>
       <c r="E33">
-        <v>-298.519</v>
+        <v>-279.568</v>
       </c>
       <c r="F33">
-        <v>587.481</v>
+        <v>606.432</v>
       </c>
       <c r="G33">
         <v>62</v>
@@ -4127,28 +4127,28 @@
         <v>176.225</v>
       </c>
       <c r="M33">
-        <v>32.4876993</v>
+        <v>33.5356896</v>
       </c>
       <c r="N33">
-        <v>143.7373007</v>
+        <v>142.6893104</v>
       </c>
       <c r="O33">
-        <v>29.6098839442</v>
+        <v>29.3939979424</v>
       </c>
       <c r="P33">
-        <v>114.1274167558</v>
+        <v>113.2953124576</v>
       </c>
       <c r="Q33">
-        <v>196.0274167558</v>
+        <v>195.1953124576</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08755405676850192</v>
+        <v>0.08807485495659015</v>
       </c>
       <c r="T33">
-        <v>0.9642969230600903</v>
+        <v>0.976324594840419</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.424360721043733</v>
+        <v>5.254849448511115</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07394152537048129</v>
+        <v>0.07385920957069628</v>
       </c>
       <c r="C34">
-        <v>1124.937054436926</v>
+        <v>1110.883392991888</v>
       </c>
       <c r="D34">
-        <v>1669.369054436926</v>
+        <v>1674.266392991888</v>
       </c>
       <c r="E34">
-        <v>-279.568</v>
+        <v>-260.617</v>
       </c>
       <c r="F34">
-        <v>606.432</v>
+        <v>625.383</v>
       </c>
       <c r="G34">
         <v>62</v>
@@ -4209,28 +4209,28 @@
         <v>176.225</v>
       </c>
       <c r="M34">
-        <v>33.5356896</v>
+        <v>34.5836799</v>
       </c>
       <c r="N34">
-        <v>142.6893104</v>
+        <v>141.6413201</v>
       </c>
       <c r="O34">
-        <v>29.3939979424</v>
+        <v>29.1781119406</v>
       </c>
       <c r="P34">
-        <v>113.2953124576</v>
+        <v>112.4632081594</v>
       </c>
       <c r="Q34">
-        <v>195.1953124576</v>
+        <v>194.3632081594</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08807485495659015</v>
+        <v>0.08861119935924819</v>
       </c>
       <c r="T34">
-        <v>0.976324594840419</v>
+        <v>0.988711301599265</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.254849448511115</v>
+        <v>5.095611586435022</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07385920957069628</v>
+        <v>0.07377689377091125</v>
       </c>
       <c r="C35">
-        <v>1110.883392991888</v>
+        <v>1096.858550210086</v>
       </c>
       <c r="D35">
-        <v>1674.266392991888</v>
+        <v>1679.192550210086</v>
       </c>
       <c r="E35">
-        <v>-260.617</v>
+        <v>-241.6659999999999</v>
       </c>
       <c r="F35">
-        <v>625.383</v>
+        <v>644.3340000000001</v>
       </c>
       <c r="G35">
         <v>62</v>
@@ -4291,28 +4291,28 @@
         <v>176.225</v>
       </c>
       <c r="M35">
-        <v>34.5836799</v>
+        <v>35.6316702</v>
       </c>
       <c r="N35">
-        <v>141.6413201</v>
+        <v>140.5933298</v>
       </c>
       <c r="O35">
-        <v>29.1781119406</v>
+        <v>28.9622259388</v>
       </c>
       <c r="P35">
-        <v>112.4632081594</v>
+        <v>111.6311038612</v>
       </c>
       <c r="Q35">
-        <v>194.3632081594</v>
+        <v>193.5311038612</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08861119935924819</v>
+        <v>0.08916379662259281</v>
       </c>
       <c r="T35">
-        <v>0.988711301599265</v>
+        <v>1.001473363108379</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.095611586435022</v>
+        <v>4.945740657422228</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07377689377091125</v>
+        <v>0.07369457797112623</v>
       </c>
       <c r="C36">
-        <v>1096.858550210086</v>
+        <v>1082.862781219734</v>
       </c>
       <c r="D36">
-        <v>1679.192550210086</v>
+        <v>1684.147781219734</v>
       </c>
       <c r="E36">
-        <v>-241.6659999999999</v>
+        <v>-222.7149999999999</v>
       </c>
       <c r="F36">
-        <v>644.3340000000001</v>
+        <v>663.2850000000001</v>
       </c>
       <c r="G36">
         <v>62</v>
@@ -4373,28 +4373,28 @@
         <v>176.225</v>
       </c>
       <c r="M36">
-        <v>35.6316702</v>
+        <v>36.6796605</v>
       </c>
       <c r="N36">
-        <v>140.5933298</v>
+        <v>139.5453395</v>
       </c>
       <c r="O36">
-        <v>28.9622259388</v>
+        <v>28.746339937</v>
       </c>
       <c r="P36">
-        <v>111.6311038612</v>
+        <v>110.798999563</v>
       </c>
       <c r="Q36">
-        <v>193.5311038612</v>
+        <v>192.698999563</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08916379662259281</v>
+        <v>0.08973339687865575</v>
       </c>
       <c r="T36">
-        <v>1.001473363108379</v>
+        <v>1.014628103433158</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.945740657422228</v>
+        <v>4.804433781495877</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07369457797112623</v>
+        <v>0.0736122621713412</v>
       </c>
       <c r="C37">
-        <v>1082.862781219734</v>
+        <v>1068.896344169459</v>
       </c>
       <c r="D37">
-        <v>1684.147781219734</v>
+        <v>1689.132344169459</v>
       </c>
       <c r="E37">
-        <v>-222.7149999999999</v>
+        <v>-203.7639999999999</v>
       </c>
       <c r="F37">
-        <v>663.2850000000001</v>
+        <v>682.2360000000001</v>
       </c>
       <c r="G37">
         <v>62</v>
@@ -4455,28 +4455,28 @@
         <v>176.225</v>
       </c>
       <c r="M37">
-        <v>36.6796605</v>
+        <v>37.72765080000001</v>
       </c>
       <c r="N37">
-        <v>139.5453395</v>
+        <v>138.4973492</v>
       </c>
       <c r="O37">
-        <v>28.746339937</v>
+        <v>28.5304539352</v>
       </c>
       <c r="P37">
-        <v>110.798999563</v>
+        <v>109.9668952648</v>
       </c>
       <c r="Q37">
-        <v>192.698999563</v>
+        <v>191.8668952648</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08973339687865575</v>
+        <v>0.09032079714272065</v>
       </c>
       <c r="T37">
-        <v>1.014628103433158</v>
+        <v>1.028193929393087</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.804433781495877</v>
+        <v>4.670977287565436</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07361226217134122</v>
+        <v>0.0735299463715562</v>
       </c>
       <c r="C38">
-        <v>1068.896344169458</v>
+        <v>1054.959500273116</v>
       </c>
       <c r="D38">
-        <v>1689.132344169458</v>
+        <v>1694.146500273116</v>
       </c>
       <c r="E38">
-        <v>-203.764</v>
+        <v>-184.813</v>
       </c>
       <c r="F38">
-        <v>682.236</v>
+        <v>701.187</v>
       </c>
       <c r="G38">
         <v>62</v>
@@ -4537,28 +4537,28 @@
         <v>176.225</v>
       </c>
       <c r="M38">
-        <v>37.7276508</v>
+        <v>38.7756411</v>
       </c>
       <c r="N38">
-        <v>138.4973492</v>
+        <v>137.4493589</v>
       </c>
       <c r="O38">
-        <v>28.5304539352</v>
+        <v>28.3145679334</v>
       </c>
       <c r="P38">
-        <v>109.9668952648</v>
+        <v>109.1347909666</v>
       </c>
       <c r="Q38">
-        <v>191.8668952648</v>
+        <v>191.0347909666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09032079714272065</v>
+        <v>0.09092684503421619</v>
       </c>
       <c r="T38">
-        <v>1.028193929393087</v>
+        <v>1.0421904164946</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.670977287565437</v>
+        <v>4.544734658171777</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0735299463715562</v>
+        <v>0.07420193057177119</v>
       </c>
       <c r="C39">
-        <v>1054.959500273116</v>
+        <v>995.9253207809254</v>
       </c>
       <c r="D39">
-        <v>1694.146500273116</v>
+        <v>1654.063320780925</v>
       </c>
       <c r="E39">
-        <v>-184.813</v>
+        <v>-165.8620000000001</v>
       </c>
       <c r="F39">
-        <v>701.187</v>
+        <v>720.1379999999999</v>
       </c>
       <c r="G39">
         <v>62</v>
@@ -4619,45 +4619,45 @@
         <v>176.225</v>
       </c>
       <c r="M39">
-        <v>38.7756411</v>
+        <v>41.6239764</v>
       </c>
       <c r="N39">
-        <v>137.4493589</v>
+        <v>134.6010236</v>
       </c>
       <c r="O39">
-        <v>28.3145679334</v>
+        <v>27.7278108616</v>
       </c>
       <c r="P39">
-        <v>109.1347909666</v>
+        <v>106.8732127384</v>
       </c>
       <c r="Q39">
-        <v>191.0347909666</v>
+        <v>188.7732127384</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09092684503421619</v>
+        <v>0.09155244285769545</v>
       </c>
       <c r="T39">
-        <v>1.0421904164946</v>
+        <v>1.056638403180034</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.206</v>
       </c>
       <c r="W39">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.544734658171777</v>
+        <v>4.23373774544039</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07420193057177119</v>
+        <v>0.07413946477198617</v>
       </c>
       <c r="C40">
-        <v>995.9253207809254</v>
+        <v>980.6202043238557</v>
       </c>
       <c r="D40">
-        <v>1654.063320780925</v>
+        <v>1657.709204323856</v>
       </c>
       <c r="E40">
-        <v>-165.8620000000001</v>
+        <v>-146.9110000000001</v>
       </c>
       <c r="F40">
-        <v>720.1379999999999</v>
+        <v>739.0889999999999</v>
       </c>
       <c r="G40">
         <v>62</v>
@@ -4701,28 +4701,28 @@
         <v>176.225</v>
       </c>
       <c r="M40">
-        <v>41.6239764</v>
+        <v>42.7193442</v>
       </c>
       <c r="N40">
-        <v>134.6010236</v>
+        <v>133.5056558</v>
       </c>
       <c r="O40">
-        <v>27.7278108616</v>
+        <v>27.5021650948</v>
       </c>
       <c r="P40">
-        <v>106.8732127384</v>
+        <v>106.0034907052</v>
       </c>
       <c r="Q40">
-        <v>188.7732127384</v>
+        <v>187.9034907052</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09155244285769545</v>
+        <v>0.09219855208522323</v>
       </c>
       <c r="T40">
-        <v>1.056638403180034</v>
+        <v>1.071560094346957</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.23373774544039</v>
+        <v>4.125180367352175</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07413946477198617</v>
+        <v>0.07407699897220114</v>
       </c>
       <c r="C41">
-        <v>980.6202043238557</v>
+        <v>965.3311958725658</v>
       </c>
       <c r="D41">
-        <v>1657.709204323856</v>
+        <v>1661.371195872566</v>
       </c>
       <c r="E41">
-        <v>-146.9110000000001</v>
+        <v>-127.96</v>
       </c>
       <c r="F41">
-        <v>739.0889999999999</v>
+        <v>758.04</v>
       </c>
       <c r="G41">
         <v>62</v>
@@ -4783,28 +4783,28 @@
         <v>176.225</v>
       </c>
       <c r="M41">
-        <v>42.7193442</v>
+        <v>43.814712</v>
       </c>
       <c r="N41">
-        <v>133.5056558</v>
+        <v>132.410288</v>
       </c>
       <c r="O41">
-        <v>27.5021650948</v>
+        <v>27.276519328</v>
       </c>
       <c r="P41">
-        <v>106.0034907052</v>
+        <v>105.133768672</v>
       </c>
       <c r="Q41">
-        <v>187.9034907052</v>
+        <v>187.033768672</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09219855208522323</v>
+        <v>0.09286619828700191</v>
       </c>
       <c r="T41">
-        <v>1.071560094346957</v>
+        <v>1.086979175219443</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.125180367352175</v>
+        <v>4.02205085816837</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07407699897220114</v>
+        <v>0.07515392317241612</v>
       </c>
       <c r="C42">
-        <v>965.3311958725658</v>
+        <v>885.4285187878297</v>
       </c>
       <c r="D42">
-        <v>1661.371195872566</v>
+        <v>1600.41951878783</v>
       </c>
       <c r="E42">
-        <v>-127.96</v>
+        <v>-109.009</v>
       </c>
       <c r="F42">
-        <v>758.04</v>
+        <v>776.991</v>
       </c>
       <c r="G42">
         <v>62</v>
@@ -4865,45 +4865,45 @@
         <v>176.225</v>
       </c>
       <c r="M42">
-        <v>43.814712</v>
+        <v>47.6295483</v>
       </c>
       <c r="N42">
-        <v>132.410288</v>
+        <v>128.5954517</v>
       </c>
       <c r="O42">
-        <v>27.276519328</v>
+        <v>26.49066305020001</v>
       </c>
       <c r="P42">
-        <v>105.133768672</v>
+        <v>102.1047886498</v>
       </c>
       <c r="Q42">
-        <v>187.033768672</v>
+        <v>184.0047886498</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09286619828700191</v>
+        <v>0.09355647656341716</v>
       </c>
       <c r="T42">
-        <v>1.086979175219443</v>
+        <v>1.102920936799472</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.206</v>
       </c>
       <c r="W42">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.02205085816837</v>
+        <v>3.699909117130973</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07515392317241612</v>
+        <v>0.07511924737263109</v>
       </c>
       <c r="C43">
-        <v>885.4285187878297</v>
+        <v>868.3703309088305</v>
       </c>
       <c r="D43">
-        <v>1600.41951878783</v>
+        <v>1602.312330908831</v>
       </c>
       <c r="E43">
-        <v>-109.009</v>
+        <v>-90.05799999999999</v>
       </c>
       <c r="F43">
-        <v>776.991</v>
+        <v>795.942</v>
       </c>
       <c r="G43">
         <v>62</v>
@@ -4947,28 +4947,28 @@
         <v>176.225</v>
       </c>
       <c r="M43">
-        <v>47.6295483</v>
+        <v>48.7912446</v>
       </c>
       <c r="N43">
-        <v>128.5954517</v>
+        <v>127.4337554</v>
       </c>
       <c r="O43">
-        <v>26.49066305020001</v>
+        <v>26.2513536124</v>
       </c>
       <c r="P43">
-        <v>102.1047886498</v>
+        <v>101.1824017876</v>
       </c>
       <c r="Q43">
-        <v>184.0047886498</v>
+        <v>183.0824017876</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09355647656341716</v>
+        <v>0.09427055753901914</v>
       </c>
       <c r="T43">
-        <v>1.102920936799472</v>
+        <v>1.119412414296054</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.699909117130973</v>
+        <v>3.611816042913568</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07511924737263111</v>
+        <v>0.07508457157284608</v>
       </c>
       <c r="C44">
-        <v>868.3703309088297</v>
+        <v>851.3166255795564</v>
       </c>
       <c r="D44">
-        <v>1602.31233090883</v>
+        <v>1604.209625579556</v>
       </c>
       <c r="E44">
-        <v>-90.05800000000011</v>
+        <v>-71.10700000000008</v>
       </c>
       <c r="F44">
-        <v>795.9419999999999</v>
+        <v>814.8929999999999</v>
       </c>
       <c r="G44">
         <v>62</v>
@@ -5029,28 +5029,28 @@
         <v>176.225</v>
       </c>
       <c r="M44">
-        <v>48.79124459999999</v>
+        <v>49.95294089999999</v>
       </c>
       <c r="N44">
-        <v>127.4337554</v>
+        <v>126.2720591</v>
       </c>
       <c r="O44">
-        <v>26.2513536124</v>
+        <v>26.0120441746</v>
       </c>
       <c r="P44">
-        <v>101.1824017876</v>
+        <v>100.2600149254</v>
       </c>
       <c r="Q44">
-        <v>183.0824017876</v>
+        <v>182.1600149254</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09427055753901914</v>
+        <v>0.09500969398744925</v>
       </c>
       <c r="T44">
-        <v>1.119412414296054</v>
+        <v>1.136482540125849</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.611816042913568</v>
+        <v>3.527820320985346</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07508457157284608</v>
+        <v>0.07602810377306107</v>
       </c>
       <c r="C45">
-        <v>851.3166255795564</v>
+        <v>782.292241916699</v>
       </c>
       <c r="D45">
-        <v>1604.209625579556</v>
+        <v>1554.136241916699</v>
       </c>
       <c r="E45">
-        <v>-71.10700000000008</v>
+        <v>-52.15600000000006</v>
       </c>
       <c r="F45">
-        <v>814.8929999999999</v>
+        <v>833.8439999999999</v>
       </c>
       <c r="G45">
         <v>62</v>
@@ -5111,45 +5111,45 @@
         <v>176.225</v>
       </c>
       <c r="M45">
-        <v>49.95294089999999</v>
+        <v>53.4494004</v>
       </c>
       <c r="N45">
-        <v>126.2720591</v>
+        <v>122.7755996</v>
       </c>
       <c r="O45">
-        <v>26.0120441746</v>
+        <v>25.2917735176</v>
       </c>
       <c r="P45">
-        <v>100.2600149254</v>
+        <v>97.48382608239999</v>
       </c>
       <c r="Q45">
-        <v>182.1600149254</v>
+        <v>179.3838260824</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09500969398744925</v>
+        <v>0.09577522816618046</v>
       </c>
       <c r="T45">
-        <v>1.136482540125849</v>
+        <v>1.154162313306708</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.206</v>
       </c>
       <c r="W45">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.527820320985346</v>
+        <v>3.297043534280695</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07602810377306107</v>
+        <v>0.07601565997327606</v>
       </c>
       <c r="C46">
-        <v>782.292241916699</v>
+        <v>763.9812861934137</v>
       </c>
       <c r="D46">
-        <v>1554.136241916699</v>
+        <v>1554.776286193414</v>
       </c>
       <c r="E46">
-        <v>-52.15600000000006</v>
+        <v>-33.20500000000004</v>
       </c>
       <c r="F46">
-        <v>833.8439999999999</v>
+        <v>852.795</v>
       </c>
       <c r="G46">
         <v>62</v>
@@ -5193,28 +5193,28 @@
         <v>176.225</v>
       </c>
       <c r="M46">
-        <v>53.4494004</v>
+        <v>54.6641595</v>
       </c>
       <c r="N46">
-        <v>122.7755996</v>
+        <v>121.5608405</v>
       </c>
       <c r="O46">
-        <v>25.2917735176</v>
+        <v>25.041533143</v>
       </c>
       <c r="P46">
-        <v>97.48382608239999</v>
+        <v>96.51930735699999</v>
       </c>
       <c r="Q46">
-        <v>179.3838260824</v>
+        <v>178.419307357</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09577522816618046</v>
+        <v>0.09656859995141098</v>
       </c>
       <c r="T46">
-        <v>1.154162313306708</v>
+        <v>1.172484987330507</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.297043534280695</v>
+        <v>3.223775900185568</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07601565997327606</v>
+        <v>0.07600321617349103</v>
       </c>
       <c r="C47">
-        <v>763.9812861934137</v>
+        <v>745.67085786978</v>
       </c>
       <c r="D47">
-        <v>1554.776286193414</v>
+        <v>1555.41685786978</v>
       </c>
       <c r="E47">
-        <v>-33.20500000000004</v>
+        <v>-14.25400000000002</v>
       </c>
       <c r="F47">
-        <v>852.795</v>
+        <v>871.746</v>
       </c>
       <c r="G47">
         <v>62</v>
@@ -5275,28 +5275,28 @@
         <v>176.225</v>
       </c>
       <c r="M47">
-        <v>54.6641595</v>
+        <v>55.87891860000001</v>
       </c>
       <c r="N47">
-        <v>121.5608405</v>
+        <v>120.3460814</v>
       </c>
       <c r="O47">
-        <v>25.041533143</v>
+        <v>24.7912927684</v>
       </c>
       <c r="P47">
-        <v>96.51930735699999</v>
+        <v>95.55478863159999</v>
       </c>
       <c r="Q47">
-        <v>178.419307357</v>
+        <v>177.4547886316</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09656859995141098</v>
+        <v>0.09739135587683521</v>
       </c>
       <c r="T47">
-        <v>1.172484987330507</v>
+        <v>1.191486278910744</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.223775900185568</v>
+        <v>3.153693815398925</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07600321617349103</v>
+        <v>0.07599077237370601</v>
       </c>
       <c r="C48">
-        <v>745.67085786978</v>
+        <v>727.360957597935</v>
       </c>
       <c r="D48">
-        <v>1555.41685786978</v>
+        <v>1556.057957597935</v>
       </c>
       <c r="E48">
-        <v>-14.25400000000002</v>
+        <v>4.697000000000003</v>
       </c>
       <c r="F48">
-        <v>871.746</v>
+        <v>890.697</v>
       </c>
       <c r="G48">
         <v>62</v>
@@ -5357,28 +5357,28 @@
         <v>176.225</v>
       </c>
       <c r="M48">
-        <v>55.87891860000001</v>
+        <v>57.0936777</v>
       </c>
       <c r="N48">
-        <v>120.3460814</v>
+        <v>119.1313223</v>
       </c>
       <c r="O48">
-        <v>24.7912927684</v>
+        <v>24.5410523938</v>
       </c>
       <c r="P48">
-        <v>95.55478863159999</v>
+        <v>94.59026990619999</v>
       </c>
       <c r="Q48">
-        <v>177.4547886316</v>
+        <v>176.4902699062</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09739135587683521</v>
+        <v>0.0982451591956717</v>
       </c>
       <c r="T48">
-        <v>1.191486278910744</v>
+        <v>1.211204600361933</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.153693815398925</v>
+        <v>3.086593946986183</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07599077237370601</v>
+        <v>0.07597832857392099</v>
       </c>
       <c r="C49">
-        <v>727.360957597935</v>
+        <v>709.0515860310935</v>
       </c>
       <c r="D49">
-        <v>1556.057957597935</v>
+        <v>1556.699586031094</v>
       </c>
       <c r="E49">
-        <v>4.697000000000003</v>
+        <v>23.64800000000002</v>
       </c>
       <c r="F49">
-        <v>890.697</v>
+        <v>909.648</v>
       </c>
       <c r="G49">
         <v>62</v>
@@ -5439,28 +5439,28 @@
         <v>176.225</v>
       </c>
       <c r="M49">
-        <v>57.0936777</v>
+        <v>58.3084368</v>
       </c>
       <c r="N49">
-        <v>119.1313223</v>
+        <v>117.9165632</v>
       </c>
       <c r="O49">
-        <v>24.5410523938</v>
+        <v>24.2908120192</v>
       </c>
       <c r="P49">
-        <v>94.59026990619999</v>
+        <v>93.62575118079999</v>
       </c>
       <c r="Q49">
-        <v>176.4902699062</v>
+        <v>175.5257511808</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0982451591956717</v>
+        <v>0.0991318011036942</v>
       </c>
       <c r="T49">
-        <v>1.211204600361933</v>
+        <v>1.231681318792014</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.086593946986183</v>
+        <v>3.02228990642397</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07597832857392098</v>
+        <v>0.07900055277413597</v>
       </c>
       <c r="C50">
-        <v>709.0515860310943</v>
+        <v>548.3952598163785</v>
       </c>
       <c r="D50">
-        <v>1556.699586031094</v>
+        <v>1414.994259816378</v>
       </c>
       <c r="E50">
-        <v>23.64799999999991</v>
+        <v>42.59899999999993</v>
       </c>
       <c r="F50">
-        <v>909.6479999999999</v>
+        <v>928.5989999999999</v>
       </c>
       <c r="G50">
         <v>62</v>
@@ -5521,45 +5521,45 @@
         <v>176.225</v>
       </c>
       <c r="M50">
-        <v>58.3084368</v>
+        <v>66.7662681</v>
       </c>
       <c r="N50">
-        <v>117.9165632</v>
+        <v>109.4587319</v>
       </c>
       <c r="O50">
-        <v>24.2908120192</v>
+        <v>22.5484987714</v>
       </c>
       <c r="P50">
-        <v>93.62575118079999</v>
+        <v>86.9102331286</v>
       </c>
       <c r="Q50">
-        <v>175.5257511808</v>
+        <v>168.8102331286</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09913180110369418</v>
+        <v>0.1000532132826195</v>
       </c>
       <c r="T50">
-        <v>1.231681318792013</v>
+        <v>1.25296104578798</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.206</v>
       </c>
       <c r="W50">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.022289906423971</v>
+        <v>2.639431632393424</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07900055277413597</v>
+        <v>0.07905004097435095</v>
       </c>
       <c r="C51">
-        <v>548.3952598163785</v>
+        <v>527.3382317580413</v>
       </c>
       <c r="D51">
-        <v>1414.994259816378</v>
+        <v>1412.888231758041</v>
       </c>
       <c r="E51">
-        <v>42.59899999999993</v>
+        <v>61.54999999999995</v>
       </c>
       <c r="F51">
-        <v>928.5989999999999</v>
+        <v>947.55</v>
       </c>
       <c r="G51">
         <v>62</v>
@@ -5603,28 +5603,28 @@
         <v>176.225</v>
       </c>
       <c r="M51">
-        <v>66.7662681</v>
+        <v>68.128845</v>
       </c>
       <c r="N51">
-        <v>109.4587319</v>
+        <v>108.096155</v>
       </c>
       <c r="O51">
-        <v>22.5484987714</v>
+        <v>22.26780793</v>
       </c>
       <c r="P51">
-        <v>86.9102331286</v>
+        <v>85.82834706999999</v>
       </c>
       <c r="Q51">
-        <v>168.8102331286</v>
+        <v>167.72834707</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1000532132826195</v>
+        <v>0.1010114819487019</v>
       </c>
       <c r="T51">
-        <v>1.25296104578798</v>
+        <v>1.275091961863785</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.639431632393424</v>
+        <v>2.586642999745556</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07905004097435095</v>
+        <v>0.07909952917456593</v>
       </c>
       <c r="C52">
-        <v>527.3382317580413</v>
+        <v>506.2874634601746</v>
       </c>
       <c r="D52">
-        <v>1412.888231758041</v>
+        <v>1410.788463460175</v>
       </c>
       <c r="E52">
-        <v>61.54999999999995</v>
+        <v>80.50099999999998</v>
       </c>
       <c r="F52">
-        <v>947.55</v>
+        <v>966.501</v>
       </c>
       <c r="G52">
         <v>62</v>
@@ -5685,28 +5685,28 @@
         <v>176.225</v>
       </c>
       <c r="M52">
-        <v>68.128845</v>
+        <v>69.49142190000001</v>
       </c>
       <c r="N52">
-        <v>108.096155</v>
+        <v>106.7335781</v>
       </c>
       <c r="O52">
-        <v>22.26780793</v>
+        <v>21.9871170886</v>
       </c>
       <c r="P52">
-        <v>85.82834706999999</v>
+        <v>84.74646101139999</v>
       </c>
       <c r="Q52">
-        <v>167.72834707</v>
+        <v>166.6464610114</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1010114819487019</v>
+        <v>0.1020088636215631</v>
       </c>
       <c r="T52">
-        <v>1.275091961863785</v>
+        <v>1.298126180636561</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.586642999745556</v>
+        <v>2.535924509554466</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07909952917456593</v>
+        <v>0.08075924937478091</v>
       </c>
       <c r="C53">
-        <v>506.2874634601746</v>
+        <v>420.3580771128914</v>
       </c>
       <c r="D53">
-        <v>1410.788463460175</v>
+        <v>1343.810077112891</v>
       </c>
       <c r="E53">
-        <v>80.50099999999998</v>
+        <v>99.452</v>
       </c>
       <c r="F53">
-        <v>966.501</v>
+        <v>985.452</v>
       </c>
       <c r="G53">
         <v>62</v>
@@ -5767,45 +5767,45 @@
         <v>176.225</v>
       </c>
       <c r="M53">
-        <v>69.49142190000001</v>
+        <v>74.6972616</v>
       </c>
       <c r="N53">
-        <v>106.7335781</v>
+        <v>101.5277384</v>
       </c>
       <c r="O53">
-        <v>21.9871170886</v>
+        <v>20.9147141104</v>
       </c>
       <c r="P53">
-        <v>84.74646101139999</v>
+        <v>80.61302428959999</v>
       </c>
       <c r="Q53">
-        <v>166.6464610114</v>
+        <v>162.5130242896</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1020088636215631</v>
+        <v>0.1030478028641269</v>
       </c>
       <c r="T53">
-        <v>1.298126180636561</v>
+        <v>1.32212015852487</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.206</v>
       </c>
       <c r="W53">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.535924509554466</v>
+        <v>2.359189563650617</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08075924937478091</v>
+        <v>0.08083970357499588</v>
       </c>
       <c r="C54">
-        <v>420.3580771128914</v>
+        <v>398.3215725576501</v>
       </c>
       <c r="D54">
-        <v>1343.810077112891</v>
+        <v>1340.72457255765</v>
       </c>
       <c r="E54">
-        <v>99.452</v>
+        <v>118.403</v>
       </c>
       <c r="F54">
-        <v>985.452</v>
+        <v>1004.403</v>
       </c>
       <c r="G54">
         <v>62</v>
@@ -5849,28 +5849,28 @@
         <v>176.225</v>
       </c>
       <c r="M54">
-        <v>74.6972616</v>
+        <v>76.1337474</v>
       </c>
       <c r="N54">
-        <v>101.5277384</v>
+        <v>100.0912526</v>
       </c>
       <c r="O54">
-        <v>20.9147141104</v>
+        <v>20.6187980356</v>
       </c>
       <c r="P54">
-        <v>80.61302428959999</v>
+        <v>79.47245456439998</v>
       </c>
       <c r="Q54">
-        <v>162.5130242896</v>
+        <v>161.3724545644</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1030478028641269</v>
+        <v>0.1041309522872253</v>
       </c>
       <c r="T54">
-        <v>1.32212015852487</v>
+        <v>1.347135156748852</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.359189563650617</v>
+        <v>2.314676553015699</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08083970357499588</v>
+        <v>0.08092015777521086</v>
       </c>
       <c r="C55">
-        <v>398.3215725576501</v>
+        <v>376.2992047157372</v>
       </c>
       <c r="D55">
-        <v>1340.72457255765</v>
+        <v>1337.653204715737</v>
       </c>
       <c r="E55">
-        <v>118.403</v>
+        <v>137.354</v>
       </c>
       <c r="F55">
-        <v>1004.403</v>
+        <v>1023.354</v>
       </c>
       <c r="G55">
         <v>62</v>
@@ -5931,28 +5931,28 @@
         <v>176.225</v>
       </c>
       <c r="M55">
-        <v>76.1337474</v>
+        <v>77.5702332</v>
       </c>
       <c r="N55">
-        <v>100.0912526</v>
+        <v>98.65476679999999</v>
       </c>
       <c r="O55">
-        <v>20.6187980356</v>
+        <v>20.3228819608</v>
       </c>
       <c r="P55">
-        <v>79.47245456439998</v>
+        <v>78.33188483919999</v>
       </c>
       <c r="Q55">
-        <v>161.3724545644</v>
+        <v>160.2318848392</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1041309522872253</v>
+        <v>0.1052611951635019</v>
       </c>
       <c r="T55">
-        <v>1.347135156748852</v>
+        <v>1.373237763591267</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.314676553015699</v>
+        <v>2.271812172404298</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08092015777521086</v>
+        <v>0.08100061197542585</v>
       </c>
       <c r="C56">
-        <v>376.2992047157372</v>
+        <v>354.2908766549197</v>
       </c>
       <c r="D56">
-        <v>1337.653204715737</v>
+        <v>1334.59587665492</v>
       </c>
       <c r="E56">
-        <v>137.354</v>
+        <v>156.3050000000001</v>
       </c>
       <c r="F56">
-        <v>1023.354</v>
+        <v>1042.305</v>
       </c>
       <c r="G56">
         <v>62</v>
@@ -6013,28 +6013,28 @@
         <v>176.225</v>
       </c>
       <c r="M56">
-        <v>77.5702332</v>
+        <v>79.00671900000002</v>
       </c>
       <c r="N56">
-        <v>98.65476679999999</v>
+        <v>97.21828099999998</v>
       </c>
       <c r="O56">
-        <v>20.3228819608</v>
+        <v>20.026965886</v>
       </c>
       <c r="P56">
-        <v>78.33188483919999</v>
+        <v>77.19131511399998</v>
       </c>
       <c r="Q56">
-        <v>160.2318848392</v>
+        <v>159.091315114</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1052611951635019</v>
+        <v>0.1064416710565019</v>
       </c>
       <c r="T56">
-        <v>1.373237763591267</v>
+        <v>1.400500486293346</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.271812172404298</v>
+        <v>2.230506496542401</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08100061197542585</v>
+        <v>0.08108106617564083</v>
       </c>
       <c r="C57">
-        <v>354.2908766549197</v>
+        <v>332.2964923271352</v>
       </c>
       <c r="D57">
-        <v>1334.59587665492</v>
+        <v>1331.552492327135</v>
       </c>
       <c r="E57">
-        <v>156.3050000000001</v>
+        <v>175.2560000000001</v>
       </c>
       <c r="F57">
-        <v>1042.305</v>
+        <v>1061.256</v>
       </c>
       <c r="G57">
         <v>62</v>
@@ -6095,28 +6095,28 @@
         <v>176.225</v>
       </c>
       <c r="M57">
-        <v>79.00671900000002</v>
+        <v>80.44320480000002</v>
       </c>
       <c r="N57">
-        <v>97.21828099999998</v>
+        <v>95.78179519999998</v>
       </c>
       <c r="O57">
-        <v>20.026965886</v>
+        <v>19.7310498112</v>
       </c>
       <c r="P57">
-        <v>77.19131511399998</v>
+        <v>76.05074538879998</v>
       </c>
       <c r="Q57">
-        <v>159.091315114</v>
+        <v>157.9507453888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1064416710565019</v>
+        <v>0.1076758049446382</v>
       </c>
       <c r="T57">
-        <v>1.400500486293346</v>
+        <v>1.429002423663701</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.230506496542401</v>
+        <v>2.190676023389858</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08108106617564083</v>
+        <v>0.08116152037585581</v>
       </c>
       <c r="C58">
-        <v>332.2964923271352</v>
+        <v>310.3159565584301</v>
       </c>
       <c r="D58">
-        <v>1331.552492327135</v>
+        <v>1328.52295655843</v>
       </c>
       <c r="E58">
-        <v>175.2560000000001</v>
+        <v>194.2070000000001</v>
       </c>
       <c r="F58">
-        <v>1061.256</v>
+        <v>1080.207</v>
       </c>
       <c r="G58">
         <v>62</v>
@@ -6177,28 +6177,28 @@
         <v>176.225</v>
       </c>
       <c r="M58">
-        <v>80.44320480000002</v>
+        <v>81.87969060000002</v>
       </c>
       <c r="N58">
-        <v>95.78179519999998</v>
+        <v>94.34530939999998</v>
       </c>
       <c r="O58">
-        <v>19.7310498112</v>
+        <v>19.4351337364</v>
       </c>
       <c r="P58">
-        <v>76.05074538879998</v>
+        <v>74.91017566359997</v>
       </c>
       <c r="Q58">
-        <v>157.9507453888</v>
+        <v>156.8101756636</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1076758049446382</v>
+        <v>0.108967340408967</v>
       </c>
       <c r="T58">
-        <v>1.429002423663701</v>
+        <v>1.458830032539653</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.190676023389858</v>
+        <v>2.152243110698808</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08116152037585581</v>
+        <v>0.0812419745760708</v>
       </c>
       <c r="C59">
-        <v>310.3159565584301</v>
+        <v>288.3491750390413</v>
       </c>
       <c r="D59">
-        <v>1328.52295655843</v>
+        <v>1325.507175039041</v>
       </c>
       <c r="E59">
-        <v>194.2070000000001</v>
+        <v>213.1580000000001</v>
       </c>
       <c r="F59">
-        <v>1080.207</v>
+        <v>1099.158</v>
       </c>
       <c r="G59">
         <v>62</v>
@@ -6259,28 +6259,28 @@
         <v>176.225</v>
       </c>
       <c r="M59">
-        <v>81.87969060000002</v>
+        <v>83.31617640000002</v>
       </c>
       <c r="N59">
-        <v>94.34530939999998</v>
+        <v>92.90882359999998</v>
       </c>
       <c r="O59">
-        <v>19.4351337364</v>
+        <v>19.1392176616</v>
       </c>
       <c r="P59">
-        <v>74.91017566359997</v>
+        <v>73.76960593839998</v>
       </c>
       <c r="Q59">
-        <v>156.8101756636</v>
+        <v>155.6696059384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.108967340408967</v>
+        <v>0.1103203775620733</v>
       </c>
       <c r="T59">
-        <v>1.458830032539653</v>
+        <v>1.490078003743032</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.152243110698808</v>
+        <v>2.115135470859173</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08124197457607078</v>
+        <v>0.08132242877628577</v>
       </c>
       <c r="C60">
-        <v>288.3491750390422</v>
+        <v>266.3960543136091</v>
       </c>
       <c r="D60">
-        <v>1325.507175039042</v>
+        <v>1322.505054313609</v>
       </c>
       <c r="E60">
-        <v>213.1579999999999</v>
+        <v>232.1089999999999</v>
       </c>
       <c r="F60">
-        <v>1099.158</v>
+        <v>1118.109</v>
       </c>
       <c r="G60">
         <v>62</v>
@@ -6341,28 +6341,28 @@
         <v>176.225</v>
       </c>
       <c r="M60">
-        <v>83.3161764</v>
+        <v>84.7526622</v>
       </c>
       <c r="N60">
-        <v>92.90882359999999</v>
+        <v>91.47233779999999</v>
       </c>
       <c r="O60">
-        <v>19.1392176616</v>
+        <v>18.8433015868</v>
       </c>
       <c r="P60">
-        <v>73.76960593839999</v>
+        <v>72.6290362132</v>
       </c>
       <c r="Q60">
-        <v>155.6696059384</v>
+        <v>154.5290362132</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1103203775620733</v>
+        <v>0.1117394165275263</v>
       </c>
       <c r="T60">
-        <v>1.490078003743032</v>
+        <v>1.522850266224624</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.115135470859174</v>
+        <v>2.079285717115798</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08132242877628577</v>
+        <v>0.08140288297650075</v>
       </c>
       <c r="C61">
-        <v>266.3960543136091</v>
+        <v>244.4565017715217</v>
       </c>
       <c r="D61">
-        <v>1322.505054313609</v>
+        <v>1319.516501771522</v>
       </c>
       <c r="E61">
-        <v>232.1089999999999</v>
+        <v>251.0599999999999</v>
       </c>
       <c r="F61">
-        <v>1118.109</v>
+        <v>1137.06</v>
       </c>
       <c r="G61">
         <v>62</v>
@@ -6423,28 +6423,28 @@
         <v>176.225</v>
       </c>
       <c r="M61">
-        <v>84.7526622</v>
+        <v>86.189148</v>
       </c>
       <c r="N61">
-        <v>91.47233779999999</v>
+        <v>90.03585199999999</v>
       </c>
       <c r="O61">
-        <v>18.8433015868</v>
+        <v>18.547385512</v>
       </c>
       <c r="P61">
-        <v>72.6290362132</v>
+        <v>71.488466488</v>
       </c>
       <c r="Q61">
-        <v>154.5290362132</v>
+        <v>153.388466488</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1117394165275263</v>
+        <v>0.1132294074412518</v>
       </c>
       <c r="T61">
-        <v>1.522850266224624</v>
+        <v>1.557261141830296</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.079285717115798</v>
+        <v>2.044630955163868</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08140288297650075</v>
+        <v>0.08148333717671574</v>
       </c>
       <c r="C62">
-        <v>244.4565017715217</v>
+        <v>222.5304256373931</v>
       </c>
       <c r="D62">
-        <v>1319.516501771522</v>
+        <v>1316.541425637393</v>
       </c>
       <c r="E62">
-        <v>251.0599999999999</v>
+        <v>270.011</v>
       </c>
       <c r="F62">
-        <v>1137.06</v>
+        <v>1156.011</v>
       </c>
       <c r="G62">
         <v>62</v>
@@ -6505,28 +6505,28 @@
         <v>176.225</v>
       </c>
       <c r="M62">
-        <v>86.189148</v>
+        <v>87.6256338</v>
       </c>
       <c r="N62">
-        <v>90.03585199999999</v>
+        <v>88.59936619999999</v>
       </c>
       <c r="O62">
-        <v>18.547385512</v>
+        <v>18.2514694372</v>
       </c>
       <c r="P62">
-        <v>71.488466488</v>
+        <v>70.34789676279999</v>
       </c>
       <c r="Q62">
-        <v>153.388466488</v>
+        <v>152.2478967628</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1132294074412518</v>
+        <v>0.1147958081454249</v>
       </c>
       <c r="T62">
-        <v>1.557261141830296</v>
+        <v>1.593436677723439</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.044630955163868</v>
+        <v>2.01111241491528</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08148333717671574</v>
+        <v>0.0885541673769307</v>
       </c>
       <c r="C63">
-        <v>222.5304256373931</v>
+        <v>-14.15469113677432</v>
       </c>
       <c r="D63">
-        <v>1316.541425637393</v>
+        <v>1098.807308863226</v>
       </c>
       <c r="E63">
-        <v>270.011</v>
+        <v>288.962</v>
       </c>
       <c r="F63">
-        <v>1156.011</v>
+        <v>1174.962</v>
       </c>
       <c r="G63">
         <v>62</v>
@@ -6587,45 +6587,45 @@
         <v>176.225</v>
       </c>
       <c r="M63">
-        <v>87.6256338</v>
+        <v>105.74658</v>
       </c>
       <c r="N63">
-        <v>88.59936619999999</v>
+        <v>70.47842</v>
       </c>
       <c r="O63">
-        <v>18.2514694372</v>
+        <v>14.51855452</v>
       </c>
       <c r="P63">
-        <v>70.34789676279999</v>
+        <v>55.95986548</v>
       </c>
       <c r="Q63">
-        <v>152.2478967628</v>
+        <v>137.85986548</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1147958081454249</v>
+        <v>0.1164446509919229</v>
       </c>
       <c r="T63">
-        <v>1.593436677723439</v>
+        <v>1.631516189189905</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.206</v>
       </c>
       <c r="W63">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.01111241491528</v>
+        <v>1.666484154853991</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0885541673769307</v>
+        <v>0.08874736957714568</v>
       </c>
       <c r="C64">
-        <v>-14.15469113677432</v>
+        <v>-38.04876429293927</v>
       </c>
       <c r="D64">
-        <v>1098.807308863226</v>
+        <v>1093.864235707061</v>
       </c>
       <c r="E64">
-        <v>288.962</v>
+        <v>307.913</v>
       </c>
       <c r="F64">
-        <v>1174.962</v>
+        <v>1193.913</v>
       </c>
       <c r="G64">
         <v>62</v>
@@ -6669,28 +6669,28 @@
         <v>176.225</v>
       </c>
       <c r="M64">
-        <v>105.74658</v>
+        <v>107.45217</v>
       </c>
       <c r="N64">
-        <v>70.47842</v>
+        <v>68.77283</v>
       </c>
       <c r="O64">
-        <v>14.51855452</v>
+        <v>14.16720298</v>
       </c>
       <c r="P64">
-        <v>55.95986548</v>
+        <v>54.60562702</v>
       </c>
       <c r="Q64">
-        <v>137.85986548</v>
+        <v>136.50562702</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1164446509919229</v>
+        <v>0.1181826204787721</v>
       </c>
       <c r="T64">
-        <v>1.631516189189905</v>
+        <v>1.671654052627531</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.666484154853991</v>
+        <v>1.640032025411865</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08874736957714568</v>
+        <v>0.08894057177736067</v>
       </c>
       <c r="C65">
-        <v>-38.04876429293927</v>
+        <v>-61.8985629960664</v>
       </c>
       <c r="D65">
-        <v>1093.864235707061</v>
+        <v>1088.965437003934</v>
       </c>
       <c r="E65">
-        <v>307.913</v>
+        <v>326.864</v>
       </c>
       <c r="F65">
-        <v>1193.913</v>
+        <v>1212.864</v>
       </c>
       <c r="G65">
         <v>62</v>
@@ -6751,28 +6751,28 @@
         <v>176.225</v>
       </c>
       <c r="M65">
-        <v>107.45217</v>
+        <v>109.15776</v>
       </c>
       <c r="N65">
-        <v>68.77283</v>
+        <v>67.06724</v>
       </c>
       <c r="O65">
-        <v>14.16720298</v>
+        <v>13.81585144</v>
       </c>
       <c r="P65">
-        <v>54.60562702</v>
+        <v>53.25138856</v>
       </c>
       <c r="Q65">
-        <v>136.50562702</v>
+        <v>135.15138856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1181826204787721</v>
+        <v>0.1200171438260018</v>
       </c>
       <c r="T65">
-        <v>1.671654052627531</v>
+        <v>1.714021797367248</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.640032025411865</v>
+        <v>1.614406525014804</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08894057177736067</v>
+        <v>0.08913377397757563</v>
       </c>
       <c r="C66">
-        <v>-61.8985629960664</v>
+        <v>-85.70467943471499</v>
       </c>
       <c r="D66">
-        <v>1088.965437003934</v>
+        <v>1084.110320565285</v>
       </c>
       <c r="E66">
-        <v>326.864</v>
+        <v>345.8150000000001</v>
       </c>
       <c r="F66">
-        <v>1212.864</v>
+        <v>1231.815</v>
       </c>
       <c r="G66">
         <v>62</v>
@@ -6833,28 +6833,28 @@
         <v>176.225</v>
       </c>
       <c r="M66">
-        <v>109.15776</v>
+        <v>110.86335</v>
       </c>
       <c r="N66">
-        <v>67.06724</v>
+        <v>65.36165</v>
       </c>
       <c r="O66">
-        <v>13.81585144</v>
+        <v>13.4644999</v>
       </c>
       <c r="P66">
-        <v>53.25138856</v>
+        <v>51.8971501</v>
       </c>
       <c r="Q66">
-        <v>135.15138856</v>
+        <v>133.7971501</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1200171438260018</v>
+        <v>0.1219564970787876</v>
       </c>
       <c r="T66">
-        <v>1.714021797367248</v>
+        <v>1.758810556092091</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.614406525014804</v>
+        <v>1.589569501553038</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08913377397757563</v>
+        <v>0.08932697617779062</v>
       </c>
       <c r="C67">
-        <v>-85.70467943471499</v>
+        <v>-109.4676952833111</v>
       </c>
       <c r="D67">
-        <v>1084.110320565285</v>
+        <v>1079.298304716689</v>
       </c>
       <c r="E67">
-        <v>345.8150000000001</v>
+        <v>364.7660000000001</v>
       </c>
       <c r="F67">
-        <v>1231.815</v>
+        <v>1250.766</v>
       </c>
       <c r="G67">
         <v>62</v>
@@ -6915,28 +6915,28 @@
         <v>176.225</v>
       </c>
       <c r="M67">
-        <v>110.86335</v>
+        <v>112.56894</v>
       </c>
       <c r="N67">
-        <v>65.36165</v>
+        <v>63.65606</v>
       </c>
       <c r="O67">
-        <v>13.4644999</v>
+        <v>13.11314836</v>
       </c>
       <c r="P67">
-        <v>51.8971501</v>
+        <v>50.54291164</v>
       </c>
       <c r="Q67">
-        <v>133.7971501</v>
+        <v>132.44291164</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1219564970787876</v>
+        <v>0.1240099299346783</v>
       </c>
       <c r="T67">
-        <v>1.758810556092091</v>
+        <v>1.806233947683101</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.589569501553038</v>
+        <v>1.565485115165871</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08932697617779062</v>
+        <v>0.0895201783780056</v>
       </c>
       <c r="C68">
-        <v>-109.4676952833111</v>
+        <v>-133.1881819344558</v>
       </c>
       <c r="D68">
-        <v>1079.298304716689</v>
+        <v>1074.528818065544</v>
       </c>
       <c r="E68">
-        <v>364.7660000000001</v>
+        <v>383.7170000000001</v>
       </c>
       <c r="F68">
-        <v>1250.766</v>
+        <v>1269.717</v>
       </c>
       <c r="G68">
         <v>62</v>
@@ -6997,28 +6997,28 @@
         <v>176.225</v>
       </c>
       <c r="M68">
-        <v>112.56894</v>
+        <v>114.27453</v>
       </c>
       <c r="N68">
-        <v>63.65606</v>
+        <v>61.95047</v>
       </c>
       <c r="O68">
-        <v>13.11314836</v>
+        <v>12.76179682</v>
       </c>
       <c r="P68">
-        <v>50.54291164</v>
+        <v>49.18867317999999</v>
       </c>
       <c r="Q68">
-        <v>132.44291164</v>
+        <v>131.08867318</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1240099299346783</v>
+        <v>0.1261878132666837</v>
       </c>
       <c r="T68">
-        <v>1.806233947683101</v>
+        <v>1.856531484219022</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.565485115165871</v>
+        <v>1.542119665685783</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0895201783780056</v>
+        <v>0.08971338057822058</v>
       </c>
       <c r="C69">
-        <v>-133.1881819344558</v>
+        <v>-156.8667007251095</v>
       </c>
       <c r="D69">
-        <v>1074.528818065544</v>
+        <v>1069.801299274891</v>
       </c>
       <c r="E69">
-        <v>383.7170000000001</v>
+        <v>402.6680000000001</v>
       </c>
       <c r="F69">
-        <v>1269.717</v>
+        <v>1288.668</v>
       </c>
       <c r="G69">
         <v>62</v>
@@ -7079,28 +7079,28 @@
         <v>176.225</v>
       </c>
       <c r="M69">
-        <v>114.27453</v>
+        <v>115.98012</v>
       </c>
       <c r="N69">
-        <v>61.95047</v>
+        <v>60.24487999999999</v>
       </c>
       <c r="O69">
-        <v>12.76179682</v>
+        <v>12.41044528</v>
       </c>
       <c r="P69">
-        <v>49.18867317999999</v>
+        <v>47.83443472</v>
       </c>
       <c r="Q69">
-        <v>131.08867318</v>
+        <v>129.73443472</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1261878132666837</v>
+        <v>0.1285018143069393</v>
       </c>
       <c r="T69">
-        <v>1.856531484219022</v>
+        <v>1.909972616788437</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.542119665685783</v>
+        <v>1.519441435308051</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08971338057822058</v>
+        <v>0.123093823091991</v>
       </c>
       <c r="C70">
-        <v>-156.8667007251095</v>
+        <v>-637.8266859593078</v>
       </c>
       <c r="D70">
-        <v>1069.801299274891</v>
+        <v>607.7923140406923</v>
       </c>
       <c r="E70">
-        <v>402.6680000000001</v>
+        <v>421.6190000000001</v>
       </c>
       <c r="F70">
-        <v>1288.668</v>
+        <v>1307.619</v>
       </c>
       <c r="G70">
         <v>62</v>
@@ -7161,45 +7161,45 @@
         <v>176.225</v>
       </c>
       <c r="M70">
-        <v>115.98012</v>
+        <v>191.9584692000001</v>
       </c>
       <c r="N70">
-        <v>60.24487999999999</v>
+        <v>-15.73346920000006</v>
       </c>
       <c r="O70">
-        <v>12.41044528</v>
+        <v>-3.241094655200012</v>
       </c>
       <c r="P70">
-        <v>47.83443472</v>
+        <v>-12.49237454480005</v>
       </c>
       <c r="Q70">
-        <v>129.73443472</v>
+        <v>69.40762545519996</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1285018143069393</v>
+        <v>0.1321216940490538</v>
       </c>
       <c r="T70">
-        <v>1.909972616788437</v>
+        <v>1.993572610832651</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.206</v>
+        <v>0.1891156464796396</v>
       </c>
       <c r="W70">
-        <v>0.07146</v>
+        <v>0.1190378230967889</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.519441435308051</v>
+        <v>0.9180371188332019</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.123093823091991</v>
+        <v>0.124103823091991</v>
       </c>
       <c r="C71">
-        <v>-637.8266859593078</v>
+        <v>-664.6172806679841</v>
       </c>
       <c r="D71">
-        <v>607.7923140406923</v>
+        <v>599.952719332016</v>
       </c>
       <c r="E71">
-        <v>421.6190000000001</v>
+        <v>440.5700000000002</v>
       </c>
       <c r="F71">
-        <v>1307.619</v>
+        <v>1326.57</v>
       </c>
       <c r="G71">
         <v>62</v>
@@ -7243,37 +7243,37 @@
         <v>176.225</v>
       </c>
       <c r="M71">
-        <v>191.9584692000001</v>
+        <v>194.740476</v>
       </c>
       <c r="N71">
-        <v>-15.73346920000006</v>
+        <v>-18.51547600000004</v>
       </c>
       <c r="O71">
-        <v>-3.241094655200012</v>
+        <v>-3.814188056000007</v>
       </c>
       <c r="P71">
-        <v>-12.49237454480005</v>
+        <v>-14.70128794400003</v>
       </c>
       <c r="Q71">
-        <v>69.40762545519996</v>
+        <v>67.19871205599998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1321216940490538</v>
+        <v>0.1349990838506889</v>
       </c>
       <c r="T71">
-        <v>1.993572610832651</v>
+        <v>2.060025031193739</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1891156464796396</v>
+        <v>0.1864139943870734</v>
       </c>
       <c r="W71">
-        <v>0.1190378230967889</v>
+        <v>0.1194344256239776</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9180371188332019</v>
+        <v>0.9049223028498706</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.124103823091991</v>
+        <v>0.125113823091991</v>
       </c>
       <c r="C72">
-        <v>-664.6172806679841</v>
+        <v>-691.2082130644159</v>
       </c>
       <c r="D72">
-        <v>599.952719332016</v>
+        <v>592.3127869355843</v>
       </c>
       <c r="E72">
-        <v>440.5700000000002</v>
+        <v>459.5210000000002</v>
       </c>
       <c r="F72">
-        <v>1326.57</v>
+        <v>1345.521</v>
       </c>
       <c r="G72">
         <v>62</v>
@@ -7325,37 +7325,37 @@
         <v>176.225</v>
       </c>
       <c r="M72">
-        <v>194.740476</v>
+        <v>197.5224828</v>
       </c>
       <c r="N72">
-        <v>-18.51547600000004</v>
+        <v>-21.29748280000004</v>
       </c>
       <c r="O72">
-        <v>-3.814188056000007</v>
+        <v>-4.387281456800008</v>
       </c>
       <c r="P72">
-        <v>-14.70128794400003</v>
+        <v>-16.91020134320003</v>
       </c>
       <c r="Q72">
-        <v>67.19871205599998</v>
+        <v>64.98979865679998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1349990838506889</v>
+        <v>0.1380749143282989</v>
       </c>
       <c r="T72">
-        <v>2.060025031193739</v>
+        <v>2.131060377096972</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1864139943870734</v>
+        <v>0.183788445170354</v>
       </c>
       <c r="W72">
-        <v>0.1194344256239776</v>
+        <v>0.1198198562489921</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9049223028498706</v>
+        <v>0.8921769183026893</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.125113823091991</v>
+        <v>0.126123823091991</v>
       </c>
       <c r="C73">
-        <v>-691.2082130644154</v>
+        <v>-717.6070148718544</v>
       </c>
       <c r="D73">
-        <v>592.3127869355845</v>
+        <v>584.8649851281456</v>
       </c>
       <c r="E73">
-        <v>459.521</v>
+        <v>478.472</v>
       </c>
       <c r="F73">
-        <v>1345.521</v>
+        <v>1364.472</v>
       </c>
       <c r="G73">
         <v>62</v>
@@ -7407,37 +7407,37 @@
         <v>176.225</v>
       </c>
       <c r="M73">
-        <v>197.5224828</v>
+        <v>200.3044896</v>
       </c>
       <c r="N73">
-        <v>-21.29748280000001</v>
+        <v>-24.07948960000002</v>
       </c>
       <c r="O73">
-        <v>-4.387281456800003</v>
+        <v>-4.960374857600004</v>
       </c>
       <c r="P73">
-        <v>-16.91020134320001</v>
+        <v>-19.11911474240001</v>
       </c>
       <c r="Q73">
-        <v>64.98979865679999</v>
+        <v>62.78088525759999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1380749143282989</v>
+        <v>0.141370446982881</v>
       </c>
       <c r="T73">
-        <v>2.131060377096971</v>
+        <v>2.207169676279006</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1837884451703541</v>
+        <v>0.1812358278763213</v>
       </c>
       <c r="W73">
-        <v>0.119819856248992</v>
+        <v>0.120194580467756</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8921769183026895</v>
+        <v>0.8797855722151521</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.126123823091991</v>
+        <v>0.127133823091991</v>
       </c>
       <c r="C74">
-        <v>-717.6070148718544</v>
+        <v>-743.8208436990608</v>
       </c>
       <c r="D74">
-        <v>584.8649851281456</v>
+        <v>577.6021563009392</v>
       </c>
       <c r="E74">
-        <v>478.472</v>
+        <v>497.423</v>
       </c>
       <c r="F74">
-        <v>1364.472</v>
+        <v>1383.423</v>
       </c>
       <c r="G74">
         <v>62</v>
@@ -7489,37 +7489,37 @@
         <v>176.225</v>
       </c>
       <c r="M74">
-        <v>200.3044896</v>
+        <v>203.0864964</v>
       </c>
       <c r="N74">
-        <v>-24.07948960000002</v>
+        <v>-26.86149640000002</v>
       </c>
       <c r="O74">
-        <v>-4.960374857600004</v>
+        <v>-5.533468258400005</v>
       </c>
       <c r="P74">
-        <v>-19.11911474240001</v>
+        <v>-21.32802814160002</v>
       </c>
       <c r="Q74">
-        <v>62.78088525759999</v>
+        <v>60.57197185839999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.141370446982881</v>
+        <v>0.1449100931674321</v>
       </c>
       <c r="T74">
-        <v>2.207169676279006</v>
+        <v>2.288916701326376</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1812358278763213</v>
+        <v>0.1787531453026731</v>
       </c>
       <c r="W74">
-        <v>0.120194580467756</v>
+        <v>0.1205590382695676</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8797855722151521</v>
+        <v>0.8677337150615199</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.127133823091991</v>
+        <v>0.128143823091991</v>
       </c>
       <c r="C75">
-        <v>-743.8208436990608</v>
+        <v>-769.8565059840782</v>
       </c>
       <c r="D75">
-        <v>577.6021563009392</v>
+        <v>570.5174940159218</v>
       </c>
       <c r="E75">
-        <v>497.423</v>
+        <v>516.374</v>
       </c>
       <c r="F75">
-        <v>1383.423</v>
+        <v>1402.374</v>
       </c>
       <c r="G75">
         <v>62</v>
@@ -7571,37 +7571,37 @@
         <v>176.225</v>
       </c>
       <c r="M75">
-        <v>203.0864964</v>
+        <v>205.8685032</v>
       </c>
       <c r="N75">
-        <v>-26.86149640000002</v>
+        <v>-29.64350320000003</v>
       </c>
       <c r="O75">
-        <v>-5.533468258400005</v>
+        <v>-6.106561659200006</v>
       </c>
       <c r="P75">
-        <v>-21.32802814160002</v>
+        <v>-23.53694154080002</v>
       </c>
       <c r="Q75">
-        <v>60.57197185839999</v>
+        <v>58.36305845919998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1449100931674321</v>
+        <v>0.148722019827718</v>
       </c>
       <c r="T75">
-        <v>2.288916701326376</v>
+        <v>2.376951959069698</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1787531453026731</v>
+        <v>0.1763375622580424</v>
       </c>
       <c r="W75">
-        <v>0.1205590382695676</v>
+        <v>0.1209136458605194</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8677337150615199</v>
+        <v>0.8560075837769048</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.128143823091991</v>
+        <v>0.129153823091991</v>
       </c>
       <c r="C76">
-        <v>-769.8565059840782</v>
+        <v>-795.7204782699459</v>
       </c>
       <c r="D76">
-        <v>570.5174940159218</v>
+        <v>563.6045217300539</v>
       </c>
       <c r="E76">
-        <v>516.374</v>
+        <v>535.3249999999998</v>
       </c>
       <c r="F76">
-        <v>1402.374</v>
+        <v>1421.325</v>
       </c>
       <c r="G76">
         <v>62</v>
@@ -7653,37 +7653,37 @@
         <v>176.225</v>
       </c>
       <c r="M76">
-        <v>205.8685032</v>
+        <v>208.65051</v>
       </c>
       <c r="N76">
-        <v>-29.64350320000003</v>
+        <v>-32.42551</v>
       </c>
       <c r="O76">
-        <v>-6.106561659200006</v>
+        <v>-6.679655060000001</v>
       </c>
       <c r="P76">
-        <v>-23.53694154080002</v>
+        <v>-25.74585494</v>
       </c>
       <c r="Q76">
-        <v>58.36305845919998</v>
+        <v>56.15414506</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.148722019827718</v>
+        <v>0.1528389006208266</v>
       </c>
       <c r="T76">
-        <v>2.376951959069698</v>
+        <v>2.472030037432486</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1763375622580424</v>
+        <v>0.1739863947612685</v>
       </c>
       <c r="W76">
-        <v>0.1209136458605194</v>
+        <v>0.1212587972490458</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8560075837769048</v>
+        <v>0.8445941493265461</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.129153823091991</v>
+        <v>0.130163823091991</v>
       </c>
       <c r="C77">
-        <v>-795.7204782699459</v>
+        <v>-821.4189269521455</v>
       </c>
       <c r="D77">
-        <v>563.6045217300539</v>
+        <v>556.8570730478543</v>
       </c>
       <c r="E77">
-        <v>535.3249999999998</v>
+        <v>554.2759999999998</v>
       </c>
       <c r="F77">
-        <v>1421.325</v>
+        <v>1440.276</v>
       </c>
       <c r="G77">
         <v>62</v>
@@ -7735,37 +7735,37 @@
         <v>176.225</v>
       </c>
       <c r="M77">
-        <v>208.65051</v>
+        <v>211.4325168</v>
       </c>
       <c r="N77">
-        <v>-32.42551</v>
+        <v>-35.20751680000001</v>
       </c>
       <c r="O77">
-        <v>-6.679655060000001</v>
+        <v>-7.252748460800002</v>
       </c>
       <c r="P77">
-        <v>-25.74585494</v>
+        <v>-27.9547683392</v>
       </c>
       <c r="Q77">
-        <v>56.15414506</v>
+        <v>53.9452316608</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1528389006208266</v>
+        <v>0.1572988548133611</v>
       </c>
       <c r="T77">
-        <v>2.472030037432486</v>
+        <v>2.575031288992173</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1739863947612685</v>
+        <v>0.1716971000933571</v>
       </c>
       <c r="W77">
-        <v>0.1212587972490458</v>
+        <v>0.1215948657062952</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8445941493265461</v>
+        <v>0.8334810684143547</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.130163823091991</v>
+        <v>0.131173823091991</v>
       </c>
       <c r="C78">
-        <v>-821.4189269521455</v>
+        <v>-846.9577266243272</v>
       </c>
       <c r="D78">
-        <v>556.8570730478543</v>
+        <v>550.2692733756727</v>
       </c>
       <c r="E78">
-        <v>554.2759999999998</v>
+        <v>573.2269999999999</v>
       </c>
       <c r="F78">
-        <v>1440.276</v>
+        <v>1459.227</v>
       </c>
       <c r="G78">
         <v>62</v>
@@ -7817,37 +7817,37 @@
         <v>176.225</v>
       </c>
       <c r="M78">
-        <v>211.4325168</v>
+        <v>214.2145236</v>
       </c>
       <c r="N78">
-        <v>-35.20751680000001</v>
+        <v>-37.98952360000001</v>
       </c>
       <c r="O78">
-        <v>-7.252748460800002</v>
+        <v>-7.825841861600003</v>
       </c>
       <c r="P78">
-        <v>-27.9547683392</v>
+        <v>-30.16368173840001</v>
       </c>
       <c r="Q78">
-        <v>53.9452316608</v>
+        <v>51.7363182616</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1572988548133611</v>
+        <v>0.1621466311095942</v>
       </c>
       <c r="T78">
-        <v>2.575031288992173</v>
+        <v>2.686989171122268</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1716971000933571</v>
+        <v>0.1694672676246122</v>
       </c>
       <c r="W78">
-        <v>0.1215948657062952</v>
+        <v>0.1219222051127069</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8334810684143547</v>
+        <v>0.822656638954428</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.131173823091991</v>
+        <v>0.132183823091991</v>
       </c>
       <c r="C79">
-        <v>-846.9577266243272</v>
+        <v>-872.3424771370543</v>
       </c>
       <c r="D79">
-        <v>550.2692733756727</v>
+        <v>543.8355228629456</v>
       </c>
       <c r="E79">
-        <v>573.2269999999999</v>
+        <v>592.1779999999999</v>
       </c>
       <c r="F79">
-        <v>1459.227</v>
+        <v>1478.178</v>
       </c>
       <c r="G79">
         <v>62</v>
@@ -7899,37 +7899,37 @@
         <v>176.225</v>
       </c>
       <c r="M79">
-        <v>214.2145236</v>
+        <v>216.9965304</v>
       </c>
       <c r="N79">
-        <v>-37.98952360000001</v>
+        <v>-40.77153040000002</v>
       </c>
       <c r="O79">
-        <v>-7.825841861600003</v>
+        <v>-8.398935262400004</v>
       </c>
       <c r="P79">
-        <v>-30.16368173840001</v>
+        <v>-32.37259513760002</v>
       </c>
       <c r="Q79">
-        <v>51.7363182616</v>
+        <v>49.52740486239999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1621466311095942</v>
+        <v>0.1674351143418485</v>
       </c>
       <c r="T79">
-        <v>2.686989171122268</v>
+        <v>2.809125042536916</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1694672676246122</v>
+        <v>0.1672946103473735</v>
       </c>
       <c r="W79">
-        <v>0.1219222051127069</v>
+        <v>0.1222411512010056</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.822656638954428</v>
+        <v>0.8121097589678328</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.132183823091991</v>
+        <v>0.133193823091991</v>
       </c>
       <c r="C80">
-        <v>-872.3424771370543</v>
+        <v>-897.5785194736667</v>
       </c>
       <c r="D80">
-        <v>543.8355228629456</v>
+        <v>537.5504805263332</v>
       </c>
       <c r="E80">
-        <v>592.1779999999999</v>
+        <v>611.1289999999999</v>
       </c>
       <c r="F80">
-        <v>1478.178</v>
+        <v>1497.129</v>
       </c>
       <c r="G80">
         <v>62</v>
@@ -7981,37 +7981,37 @@
         <v>176.225</v>
       </c>
       <c r="M80">
-        <v>216.9965304</v>
+        <v>219.7785372</v>
       </c>
       <c r="N80">
-        <v>-40.77153040000002</v>
+        <v>-43.55353720000002</v>
       </c>
       <c r="O80">
-        <v>-8.398935262400004</v>
+        <v>-8.972028663200005</v>
       </c>
       <c r="P80">
-        <v>-32.37259513760002</v>
+        <v>-34.58150853680002</v>
       </c>
       <c r="Q80">
-        <v>49.52740486239999</v>
+        <v>47.31849146319999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1674351143418485</v>
+        <v>0.1732272626438413</v>
       </c>
       <c r="T80">
-        <v>2.809125042536916</v>
+        <v>2.942892901705341</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1672946103473735</v>
+        <v>0.1651769570518372</v>
       </c>
       <c r="W80">
-        <v>0.1222411512010056</v>
+        <v>0.1225520227047903</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8121097589678328</v>
+        <v>0.8018298886011512</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.133193823091991</v>
+        <v>0.1784837977615794</v>
       </c>
       <c r="C81">
-        <v>-897.5785194736667</v>
+        <v>-1100.015732993192</v>
       </c>
       <c r="D81">
-        <v>537.5504805263332</v>
+        <v>354.0642670068078</v>
       </c>
       <c r="E81">
-        <v>611.1289999999999</v>
+        <v>630.0799999999999</v>
       </c>
       <c r="F81">
-        <v>1497.129</v>
+        <v>1516.08</v>
       </c>
       <c r="G81">
         <v>62</v>
@@ -8063,45 +8063,45 @@
         <v>176.225</v>
       </c>
       <c r="M81">
-        <v>219.7785372</v>
+        <v>304.428864</v>
       </c>
       <c r="N81">
-        <v>-43.55353720000002</v>
+        <v>-128.203864</v>
       </c>
       <c r="O81">
-        <v>-8.972028663200005</v>
+        <v>-26.409995984</v>
       </c>
       <c r="P81">
-        <v>-34.58150853680002</v>
+        <v>-101.793868016</v>
       </c>
       <c r="Q81">
-        <v>47.31849146319999</v>
+        <v>-19.89386801599997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1732272626438413</v>
+        <v>0.1849984991239752</v>
       </c>
       <c r="T81">
-        <v>2.942892901705341</v>
+        <v>3.214745938198041</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1651769570518372</v>
+        <v>0.1192473983018903</v>
       </c>
       <c r="W81">
-        <v>0.1225520227047903</v>
+        <v>0.1768551224209804</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8018298886011512</v>
+        <v>0.5788708655431569</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1784837977615794</v>
+        <v>0.1800337977615794</v>
       </c>
       <c r="C82">
-        <v>-1100.015732993192</v>
+        <v>-1123.055119249203</v>
       </c>
       <c r="D82">
-        <v>354.0642670068078</v>
+        <v>349.9758807507972</v>
       </c>
       <c r="E82">
-        <v>630.0799999999999</v>
+        <v>649.0309999999999</v>
       </c>
       <c r="F82">
-        <v>1516.08</v>
+        <v>1535.031</v>
       </c>
       <c r="G82">
         <v>62</v>
@@ -8145,37 +8145,37 @@
         <v>176.225</v>
       </c>
       <c r="M82">
-        <v>304.428864</v>
+        <v>308.2342248</v>
       </c>
       <c r="N82">
-        <v>-128.203864</v>
+        <v>-132.0092248</v>
       </c>
       <c r="O82">
-        <v>-26.409995984</v>
+        <v>-27.1939003088</v>
       </c>
       <c r="P82">
-        <v>-101.793868016</v>
+        <v>-104.8153244912</v>
       </c>
       <c r="Q82">
-        <v>-19.89386801599997</v>
+        <v>-22.91532449119998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1849984991239752</v>
+        <v>0.1923247359199739</v>
       </c>
       <c r="T82">
-        <v>3.214745938198041</v>
+        <v>3.383943092840044</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1192473983018903</v>
+        <v>0.1177752081993979</v>
       </c>
       <c r="W82">
-        <v>0.1768551224209804</v>
+        <v>0.1771507381935609</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5788708655431569</v>
+        <v>0.5717243116475623</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1800337977615794</v>
+        <v>0.1815837977615794</v>
       </c>
       <c r="C83">
-        <v>-1123.055119249203</v>
+        <v>-1146.001165963953</v>
       </c>
       <c r="D83">
-        <v>349.9758807507972</v>
+        <v>345.9808340360466</v>
       </c>
       <c r="E83">
-        <v>649.0309999999999</v>
+        <v>667.982</v>
       </c>
       <c r="F83">
-        <v>1535.031</v>
+        <v>1553.982</v>
       </c>
       <c r="G83">
         <v>62</v>
@@ -8227,37 +8227,37 @@
         <v>176.225</v>
       </c>
       <c r="M83">
-        <v>308.2342248</v>
+        <v>312.0395856</v>
       </c>
       <c r="N83">
-        <v>-132.0092248</v>
+        <v>-135.8145856</v>
       </c>
       <c r="O83">
-        <v>-27.1939003088</v>
+        <v>-27.97780463360001</v>
       </c>
       <c r="P83">
-        <v>-104.8153244912</v>
+        <v>-107.8367809664</v>
       </c>
       <c r="Q83">
-        <v>-22.91532449119998</v>
+        <v>-25.93678096640001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1923247359199739</v>
+        <v>0.2004649990266391</v>
       </c>
       <c r="T83">
-        <v>3.383943092840044</v>
+        <v>3.571939931331158</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1177752081993979</v>
+        <v>0.1163389251725759</v>
       </c>
       <c r="W83">
-        <v>0.1771507381935609</v>
+        <v>0.1774391438253468</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5717243116475623</v>
+        <v>0.5647520639445434</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1815837977615794</v>
+        <v>0.1831337977615794</v>
       </c>
       <c r="C84">
-        <v>-1146.001165963953</v>
+        <v>-1168.857033531126</v>
       </c>
       <c r="D84">
-        <v>345.9808340360466</v>
+        <v>342.0759664688738</v>
       </c>
       <c r="E84">
-        <v>667.982</v>
+        <v>686.933</v>
       </c>
       <c r="F84">
-        <v>1553.982</v>
+        <v>1572.933</v>
       </c>
       <c r="G84">
         <v>62</v>
@@ -8309,37 +8309,37 @@
         <v>176.225</v>
       </c>
       <c r="M84">
-        <v>312.0395856</v>
+        <v>315.8449464</v>
       </c>
       <c r="N84">
-        <v>-135.8145856</v>
+        <v>-139.6199464</v>
       </c>
       <c r="O84">
-        <v>-27.97780463360001</v>
+        <v>-28.76170895840001</v>
       </c>
       <c r="P84">
-        <v>-107.8367809664</v>
+        <v>-110.8582374416</v>
       </c>
       <c r="Q84">
-        <v>-25.93678096640001</v>
+        <v>-28.95823744160002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2004649990266391</v>
+        <v>0.2095629401458532</v>
       </c>
       <c r="T84">
-        <v>3.571939931331158</v>
+        <v>3.782054044938873</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1163389251725759</v>
+        <v>0.114937251375316</v>
       </c>
       <c r="W84">
-        <v>0.1774391438253468</v>
+        <v>0.1777205999238366</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5647520639445434</v>
+        <v>0.5579478222102716</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1831337977615794</v>
+        <v>0.1846837977615794</v>
       </c>
       <c r="C85">
-        <v>-1168.857033531126</v>
+        <v>-1191.625741259259</v>
       </c>
       <c r="D85">
-        <v>342.0759664688738</v>
+        <v>338.2582587407415</v>
       </c>
       <c r="E85">
-        <v>686.933</v>
+        <v>705.884</v>
       </c>
       <c r="F85">
-        <v>1572.933</v>
+        <v>1591.884</v>
       </c>
       <c r="G85">
         <v>62</v>
@@ -8391,37 +8391,37 @@
         <v>176.225</v>
       </c>
       <c r="M85">
-        <v>315.8449464</v>
+        <v>319.6503072</v>
       </c>
       <c r="N85">
-        <v>-139.6199464</v>
+        <v>-143.4253072</v>
       </c>
       <c r="O85">
-        <v>-28.76170895840001</v>
+        <v>-29.5456132832</v>
       </c>
       <c r="P85">
-        <v>-110.8582374416</v>
+        <v>-113.8796939168</v>
       </c>
       <c r="Q85">
-        <v>-28.95823744160002</v>
+        <v>-31.97969391679999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2095629401458532</v>
+        <v>0.2197981239049691</v>
       </c>
       <c r="T85">
-        <v>3.782054044938873</v>
+        <v>4.018432422747553</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.114937251375316</v>
+        <v>0.1135689507637051</v>
       </c>
       <c r="W85">
-        <v>0.1777205999238366</v>
+        <v>0.177995354686648</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5579478222102716</v>
+        <v>0.551305586231578</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1846837977615794</v>
+        <v>0.1862337977615794</v>
       </c>
       <c r="C86">
-        <v>-1191.625741259258</v>
+        <v>-1214.310175157687</v>
       </c>
       <c r="D86">
-        <v>338.2582587407415</v>
+        <v>334.5248248423127</v>
       </c>
       <c r="E86">
-        <v>705.8839999999998</v>
+        <v>724.8349999999998</v>
       </c>
       <c r="F86">
-        <v>1591.884</v>
+        <v>1610.835</v>
       </c>
       <c r="G86">
         <v>62</v>
@@ -8473,37 +8473,37 @@
         <v>176.225</v>
       </c>
       <c r="M86">
-        <v>319.6503072</v>
+        <v>323.4556679999999</v>
       </c>
       <c r="N86">
-        <v>-143.4253072</v>
+        <v>-147.230668</v>
       </c>
       <c r="O86">
-        <v>-29.5456132832</v>
+        <v>-30.32951760799999</v>
       </c>
       <c r="P86">
-        <v>-113.8796939168</v>
+        <v>-116.901150392</v>
       </c>
       <c r="Q86">
-        <v>-31.97969391679999</v>
+        <v>-35.00115039199996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.219798123904969</v>
+        <v>0.2313979988319669</v>
       </c>
       <c r="T86">
-        <v>4.018432422747551</v>
+        <v>4.286327917597387</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1135689507637051</v>
+        <v>0.1122328454606027</v>
       </c>
       <c r="W86">
-        <v>0.177995354686648</v>
+        <v>0.178263644631511</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.551305586231578</v>
+        <v>0.5448196381582654</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1862337977615794</v>
+        <v>0.1877837977615794</v>
       </c>
       <c r="C87">
-        <v>-1214.310175157687</v>
+        <v>-1236.913095212511</v>
       </c>
       <c r="D87">
-        <v>334.5248248423127</v>
+        <v>330.8729047874887</v>
       </c>
       <c r="E87">
-        <v>724.8349999999998</v>
+        <v>743.7859999999998</v>
       </c>
       <c r="F87">
-        <v>1610.835</v>
+        <v>1629.786</v>
       </c>
       <c r="G87">
         <v>62</v>
@@ -8555,37 +8555,37 @@
         <v>176.225</v>
       </c>
       <c r="M87">
-        <v>323.4556679999999</v>
+        <v>327.2610288</v>
       </c>
       <c r="N87">
-        <v>-147.230668</v>
+        <v>-151.0360288</v>
       </c>
       <c r="O87">
-        <v>-30.32951760799999</v>
+        <v>-31.11342193279999</v>
       </c>
       <c r="P87">
-        <v>-116.901150392</v>
+        <v>-119.9226068672</v>
       </c>
       <c r="Q87">
-        <v>-35.00115039199996</v>
+        <v>-38.02260686719997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2313979988319669</v>
+        <v>0.244654998748536</v>
       </c>
       <c r="T87">
-        <v>4.286327917597387</v>
+        <v>4.592494197425772</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1122328454606027</v>
+        <v>0.1109278123738515</v>
       </c>
       <c r="W87">
-        <v>0.178263644631511</v>
+        <v>0.1785256952753306</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5448196381582654</v>
+        <v>0.5384845260866576</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1877837977615794</v>
+        <v>0.1893337977615794</v>
       </c>
       <c r="C88">
-        <v>-1236.913095212511</v>
+        <v>-1259.437142191122</v>
       </c>
       <c r="D88">
-        <v>330.8729047874887</v>
+        <v>327.2998578088776</v>
       </c>
       <c r="E88">
-        <v>743.7859999999998</v>
+        <v>762.7369999999999</v>
       </c>
       <c r="F88">
-        <v>1629.786</v>
+        <v>1648.737</v>
       </c>
       <c r="G88">
         <v>62</v>
@@ -8637,37 +8637,37 @@
         <v>176.225</v>
       </c>
       <c r="M88">
-        <v>327.2610288</v>
+        <v>331.0663896</v>
       </c>
       <c r="N88">
-        <v>-151.0360288</v>
+        <v>-154.8413896</v>
       </c>
       <c r="O88">
-        <v>-31.11342193279999</v>
+        <v>-31.8973262576</v>
       </c>
       <c r="P88">
-        <v>-119.9226068672</v>
+        <v>-122.9440633424</v>
       </c>
       <c r="Q88">
-        <v>-38.02260686719997</v>
+        <v>-41.04406334239998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.244654998748536</v>
+        <v>0.259951537113808</v>
       </c>
       <c r="T88">
-        <v>4.592494197425772</v>
+        <v>4.945762981843139</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1109278123738515</v>
+        <v>0.1096527800477153</v>
       </c>
       <c r="W88">
-        <v>0.1785256952753306</v>
+        <v>0.1787817217664188</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5384845260866576</v>
+        <v>0.5322950487753166</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1893337977615794</v>
+        <v>0.1908837977615794</v>
       </c>
       <c r="C89">
-        <v>-1259.437142191122</v>
+        <v>-1281.884844010559</v>
       </c>
       <c r="D89">
-        <v>327.2998578088776</v>
+        <v>323.8031559894404</v>
       </c>
       <c r="E89">
-        <v>762.7369999999999</v>
+        <v>781.6879999999999</v>
       </c>
       <c r="F89">
-        <v>1648.737</v>
+        <v>1667.688</v>
       </c>
       <c r="G89">
         <v>62</v>
@@ -8719,37 +8719,37 @@
         <v>176.225</v>
       </c>
       <c r="M89">
-        <v>331.0663896</v>
+        <v>334.8717504</v>
       </c>
       <c r="N89">
-        <v>-154.8413896</v>
+        <v>-158.6467504</v>
       </c>
       <c r="O89">
-        <v>-31.8973262576</v>
+        <v>-32.6812305824</v>
       </c>
       <c r="P89">
-        <v>-122.9440633424</v>
+        <v>-125.9655198176</v>
       </c>
       <c r="Q89">
-        <v>-41.04406334239998</v>
+        <v>-44.06551981759999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.259951537113808</v>
+        <v>0.2777974985399587</v>
       </c>
       <c r="T89">
-        <v>4.945762981843139</v>
+        <v>5.357909896996735</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1096527800477153</v>
+        <v>0.1084067257289912</v>
       </c>
       <c r="W89">
-        <v>0.1787817217664188</v>
+        <v>0.1790319294736186</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5322950487753166</v>
+        <v>0.5262462414028699</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1908837977615794</v>
+        <v>0.1924337977615794</v>
       </c>
       <c r="C90">
-        <v>-1281.884844010559</v>
+        <v>-1304.25862170196</v>
       </c>
       <c r="D90">
-        <v>323.8031559894404</v>
+        <v>320.3803782980402</v>
       </c>
       <c r="E90">
-        <v>781.6879999999999</v>
+        <v>800.6389999999999</v>
       </c>
       <c r="F90">
-        <v>1667.688</v>
+        <v>1686.639</v>
       </c>
       <c r="G90">
         <v>62</v>
@@ -8801,37 +8801,37 @@
         <v>176.225</v>
       </c>
       <c r="M90">
-        <v>334.8717504</v>
+        <v>338.6771112</v>
       </c>
       <c r="N90">
-        <v>-158.6467504</v>
+        <v>-162.4521112</v>
       </c>
       <c r="O90">
-        <v>-32.6812305824</v>
+        <v>-33.4651349072</v>
       </c>
       <c r="P90">
-        <v>-125.9655198176</v>
+        <v>-128.9869762928</v>
       </c>
       <c r="Q90">
-        <v>-44.06551981759999</v>
+        <v>-47.08697629280002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2777974985399587</v>
+        <v>0.2988881802254094</v>
       </c>
       <c r="T90">
-        <v>5.357909896996735</v>
+        <v>5.844992614905529</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1084067257289912</v>
+        <v>0.1071886726309127</v>
       </c>
       <c r="W90">
-        <v>0.1790319294736186</v>
+        <v>0.1792765145357127</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5262462414028699</v>
+        <v>0.5203333622859837</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1924337977615794</v>
+        <v>0.1939837977615794</v>
       </c>
       <c r="C91">
-        <v>-1304.25862170196</v>
+        <v>-1326.560795000683</v>
       </c>
       <c r="D91">
-        <v>320.3803782980402</v>
+        <v>317.0292049993172</v>
       </c>
       <c r="E91">
-        <v>800.6389999999999</v>
+        <v>819.5899999999999</v>
       </c>
       <c r="F91">
-        <v>1686.639</v>
+        <v>1705.59</v>
       </c>
       <c r="G91">
         <v>62</v>
@@ -8883,37 +8883,37 @@
         <v>176.225</v>
       </c>
       <c r="M91">
-        <v>338.6771112</v>
+        <v>342.482472</v>
       </c>
       <c r="N91">
-        <v>-162.4521112</v>
+        <v>-166.257472</v>
       </c>
       <c r="O91">
-        <v>-33.4651349072</v>
+        <v>-34.249039232</v>
       </c>
       <c r="P91">
-        <v>-128.9869762928</v>
+        <v>-132.008432768</v>
       </c>
       <c r="Q91">
-        <v>-47.08697629280002</v>
+        <v>-50.10843276799997</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2988881802254094</v>
+        <v>0.3241969982479504</v>
       </c>
       <c r="T91">
-        <v>5.844992614905529</v>
+        <v>6.429491876396082</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1071886726309127</v>
+        <v>0.1059976873794581</v>
       </c>
       <c r="W91">
-        <v>0.1792765145357127</v>
+        <v>0.1795156643742048</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5203333622859837</v>
+        <v>0.5145518804828062</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1939837977615794</v>
+        <v>0.1955337977615794</v>
       </c>
       <c r="C92">
-        <v>-1326.560795000683</v>
+        <v>-1348.79358758923</v>
       </c>
       <c r="D92">
-        <v>317.0292049993172</v>
+        <v>313.7474124107703</v>
       </c>
       <c r="E92">
-        <v>819.5899999999999</v>
+        <v>838.5409999999999</v>
       </c>
       <c r="F92">
-        <v>1705.59</v>
+        <v>1724.541</v>
       </c>
       <c r="G92">
         <v>62</v>
@@ -8965,37 +8965,37 @@
         <v>176.225</v>
       </c>
       <c r="M92">
-        <v>342.482472</v>
+        <v>346.2878328</v>
       </c>
       <c r="N92">
-        <v>-166.257472</v>
+        <v>-170.0628328</v>
       </c>
       <c r="O92">
-        <v>-34.249039232</v>
+        <v>-35.0329435568</v>
       </c>
       <c r="P92">
-        <v>-132.008432768</v>
+        <v>-135.0298892432</v>
       </c>
       <c r="Q92">
-        <v>-50.10843276799997</v>
+        <v>-53.12988924319998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3241969982479504</v>
+        <v>0.3551299980532783</v>
       </c>
       <c r="T92">
-        <v>6.429491876396082</v>
+        <v>7.143879862662314</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1059976873794581</v>
+        <v>0.1048328776280355</v>
       </c>
       <c r="W92">
-        <v>0.1795156643742048</v>
+        <v>0.1797495581722905</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5145518804828062</v>
+        <v>0.5088974642137643</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1955337977615794</v>
+        <v>0.1970837977615794</v>
       </c>
       <c r="C93">
-        <v>-1348.79358758923</v>
+        <v>-1370.959132017861</v>
       </c>
       <c r="D93">
-        <v>313.7474124107703</v>
+        <v>310.5328679821388</v>
       </c>
       <c r="E93">
-        <v>838.5409999999999</v>
+        <v>857.492</v>
       </c>
       <c r="F93">
-        <v>1724.541</v>
+        <v>1743.492</v>
       </c>
       <c r="G93">
         <v>62</v>
@@ -9047,37 +9047,37 @@
         <v>176.225</v>
       </c>
       <c r="M93">
-        <v>346.2878328</v>
+        <v>350.0931936</v>
       </c>
       <c r="N93">
-        <v>-170.0628328</v>
+        <v>-173.8681936</v>
       </c>
       <c r="O93">
-        <v>-35.0329435568</v>
+        <v>-35.8168478816</v>
       </c>
       <c r="P93">
-        <v>-135.0298892432</v>
+        <v>-138.0513457184</v>
       </c>
       <c r="Q93">
-        <v>-53.12988924319998</v>
+        <v>-56.15134571839999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3551299980532783</v>
+        <v>0.3937962478099382</v>
       </c>
       <c r="T93">
-        <v>7.143879862662314</v>
+        <v>8.036864845495106</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1048328776280355</v>
+        <v>0.1036933898277307</v>
       </c>
       <c r="W93">
-        <v>0.1797495581722905</v>
+        <v>0.1799783673225917</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5088974642137643</v>
+        <v>0.5033659700375277</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1970837977615794</v>
+        <v>0.2316195805854057</v>
       </c>
       <c r="C94">
-        <v>-1370.959132017861</v>
+        <v>-1447.624693930576</v>
       </c>
       <c r="D94">
-        <v>310.5328679821388</v>
+        <v>252.8183060694242</v>
       </c>
       <c r="E94">
-        <v>857.492</v>
+        <v>876.443</v>
       </c>
       <c r="F94">
-        <v>1743.492</v>
+        <v>1762.443</v>
       </c>
       <c r="G94">
         <v>62</v>
@@ -9129,45 +9129,45 @@
         <v>176.225</v>
       </c>
       <c r="M94">
-        <v>350.0931936</v>
+        <v>415.5840594</v>
       </c>
       <c r="N94">
-        <v>-173.8681936</v>
+        <v>-239.3590594</v>
       </c>
       <c r="O94">
-        <v>-35.8168478816</v>
+        <v>-49.30796623640001</v>
       </c>
       <c r="P94">
-        <v>-138.0513457184</v>
+        <v>-190.0510931636</v>
       </c>
       <c r="Q94">
-        <v>-56.15134571839999</v>
+        <v>-108.1510931636</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3937962478099382</v>
+        <v>0.4497354664088765</v>
       </c>
       <c r="T94">
-        <v>8.036864845495106</v>
+        <v>9.328763658403613</v>
       </c>
       <c r="U94">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1036933898277307</v>
+        <v>0.0873526045546876</v>
       </c>
       <c r="W94">
-        <v>0.1799783673225917</v>
+        <v>0.2152022558460047</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5033659700375277</v>
+        <v>0.4240417696829495</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2316195805854057</v>
+        <v>0.2335195805854057</v>
       </c>
       <c r="C95">
-        <v>-1447.624693930576</v>
+        <v>-1469.134589385349</v>
       </c>
       <c r="D95">
-        <v>252.8183060694242</v>
+        <v>250.259410614651</v>
       </c>
       <c r="E95">
-        <v>876.443</v>
+        <v>895.394</v>
       </c>
       <c r="F95">
-        <v>1762.443</v>
+        <v>1781.394</v>
       </c>
       <c r="G95">
         <v>62</v>
@@ -9211,37 +9211,37 @@
         <v>176.225</v>
       </c>
       <c r="M95">
-        <v>415.5840594</v>
+        <v>420.0527052</v>
       </c>
       <c r="N95">
-        <v>-239.3590594</v>
+        <v>-243.8277052</v>
       </c>
       <c r="O95">
-        <v>-49.30796623640001</v>
+        <v>-50.2285072712</v>
       </c>
       <c r="P95">
-        <v>-190.0510931636</v>
+        <v>-193.5991979288</v>
       </c>
       <c r="Q95">
-        <v>-108.1510931636</v>
+        <v>-111.6991979288</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4497354664088765</v>
+        <v>0.5170580441436894</v>
       </c>
       <c r="T95">
-        <v>9.328763658403613</v>
+        <v>10.88355760147089</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0873526045546876</v>
+        <v>0.08642332152751007</v>
       </c>
       <c r="W95">
-        <v>0.2152022558460047</v>
+        <v>0.2154213807838131</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4240417696829495</v>
+        <v>0.4195306870267479</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2335195805854057</v>
+        <v>0.2354195805854057</v>
       </c>
       <c r="C96">
-        <v>-1469.134589385349</v>
+        <v>-1490.593204256661</v>
       </c>
       <c r="D96">
-        <v>250.259410614651</v>
+        <v>247.7517957433394</v>
       </c>
       <c r="E96">
-        <v>895.394</v>
+        <v>914.345</v>
       </c>
       <c r="F96">
-        <v>1781.394</v>
+        <v>1800.345</v>
       </c>
       <c r="G96">
         <v>62</v>
@@ -9293,37 +9293,37 @@
         <v>176.225</v>
       </c>
       <c r="M96">
-        <v>420.0527052</v>
+        <v>424.521351</v>
       </c>
       <c r="N96">
-        <v>-243.8277052</v>
+        <v>-248.296351</v>
       </c>
       <c r="O96">
-        <v>-50.2285072712</v>
+        <v>-51.14904830600001</v>
       </c>
       <c r="P96">
-        <v>-193.5991979288</v>
+        <v>-197.147302694</v>
       </c>
       <c r="Q96">
-        <v>-111.6991979288</v>
+        <v>-115.247302694</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5170580441436894</v>
+        <v>0.6113096529724276</v>
       </c>
       <c r="T96">
-        <v>10.88355760147089</v>
+        <v>13.06026912176507</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08642332152751007</v>
+        <v>0.08551360235353628</v>
       </c>
       <c r="W96">
-        <v>0.2154213807838131</v>
+        <v>0.2156358925650362</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4195306870267479</v>
+        <v>0.4151145745317294</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2354195805854057</v>
+        <v>0.2373195805854057</v>
       </c>
       <c r="C97">
-        <v>-1490.593204256661</v>
+        <v>-1512.002064755694</v>
       </c>
       <c r="D97">
-        <v>247.7517957433394</v>
+        <v>245.2939352443058</v>
       </c>
       <c r="E97">
-        <v>914.345</v>
+        <v>933.296</v>
       </c>
       <c r="F97">
-        <v>1800.345</v>
+        <v>1819.296</v>
       </c>
       <c r="G97">
         <v>62</v>
@@ -9375,37 +9375,37 @@
         <v>176.225</v>
       </c>
       <c r="M97">
-        <v>424.521351</v>
+        <v>428.9899968</v>
       </c>
       <c r="N97">
-        <v>-248.296351</v>
+        <v>-252.7649968</v>
       </c>
       <c r="O97">
-        <v>-51.14904830600001</v>
+        <v>-52.06958934080001</v>
       </c>
       <c r="P97">
-        <v>-197.147302694</v>
+        <v>-200.6954074592</v>
       </c>
       <c r="Q97">
-        <v>-115.247302694</v>
+        <v>-118.7954074592</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6113096529724276</v>
+        <v>0.7526870662155347</v>
       </c>
       <c r="T97">
-        <v>13.06026912176507</v>
+        <v>16.32533640220634</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08551360235353628</v>
+        <v>0.08462283566235361</v>
       </c>
       <c r="W97">
-        <v>0.2156358925650362</v>
+        <v>0.215845935350817</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4151145745317294</v>
+        <v>0.4107904643803573</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2373195805854057</v>
+        <v>0.2392195805854057</v>
       </c>
       <c r="C98">
-        <v>-1512.002064755694</v>
+        <v>-1533.362637124497</v>
       </c>
       <c r="D98">
-        <v>245.293935244306</v>
+        <v>242.8843628755023</v>
       </c>
       <c r="E98">
-        <v>933.2959999999998</v>
+        <v>952.2469999999998</v>
       </c>
       <c r="F98">
-        <v>1819.296</v>
+        <v>1838.247</v>
       </c>
       <c r="G98">
         <v>62</v>
@@ -9457,37 +9457,37 @@
         <v>176.225</v>
       </c>
       <c r="M98">
-        <v>428.9899968</v>
+        <v>433.4586426</v>
       </c>
       <c r="N98">
-        <v>-252.7649968</v>
+        <v>-257.2336425999999</v>
       </c>
       <c r="O98">
-        <v>-52.0695893408</v>
+        <v>-52.99013037559999</v>
       </c>
       <c r="P98">
-        <v>-200.6954074592</v>
+        <v>-204.2435122244</v>
       </c>
       <c r="Q98">
-        <v>-118.7954074592</v>
+        <v>-122.3435122243999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7526870662155328</v>
+        <v>0.9883160882873772</v>
       </c>
       <c r="T98">
-        <v>16.3253364022063</v>
+        <v>21.76711520294173</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08462283566235361</v>
+        <v>0.0837504352947005</v>
       </c>
       <c r="W98">
-        <v>0.215845935350817</v>
+        <v>0.2160516473575096</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4107904643803574</v>
+        <v>0.4065555111393228</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2392195805854057</v>
+        <v>0.2411195805854057</v>
       </c>
       <c r="C99">
-        <v>-1533.362637124497</v>
+        <v>-1554.676330552777</v>
       </c>
       <c r="D99">
-        <v>242.8843628755023</v>
+        <v>240.5216694472227</v>
       </c>
       <c r="E99">
-        <v>952.2469999999998</v>
+        <v>971.1979999999999</v>
       </c>
       <c r="F99">
-        <v>1838.247</v>
+        <v>1857.198</v>
       </c>
       <c r="G99">
         <v>62</v>
@@ -9539,37 +9539,37 @@
         <v>176.225</v>
       </c>
       <c r="M99">
-        <v>433.4586426</v>
+        <v>437.9272884</v>
       </c>
       <c r="N99">
-        <v>-257.2336425999999</v>
+        <v>-261.7022884</v>
       </c>
       <c r="O99">
-        <v>-52.99013037559999</v>
+        <v>-53.91067141040001</v>
       </c>
       <c r="P99">
-        <v>-204.2435122244</v>
+        <v>-207.7916169896</v>
       </c>
       <c r="Q99">
-        <v>-122.3435122243999</v>
+        <v>-125.8916169896</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9883160882873772</v>
+        <v>1.459574132431066</v>
       </c>
       <c r="T99">
-        <v>21.76711520294173</v>
+        <v>32.6506728044126</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0837504352947005</v>
+        <v>0.08289583901618314</v>
       </c>
       <c r="W99">
-        <v>0.2160516473575096</v>
+        <v>0.216253161159984</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4065555111393228</v>
+        <v>0.402406985515452</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2411195805854057</v>
+        <v>0.2430195805854057</v>
       </c>
       <c r="C100">
-        <v>-1554.676330552777</v>
+        <v>-1575.944499926088</v>
       </c>
       <c r="D100">
-        <v>240.5216694472227</v>
+        <v>238.2045000739117</v>
       </c>
       <c r="E100">
-        <v>971.1979999999999</v>
+        <v>990.1489999999999</v>
       </c>
       <c r="F100">
-        <v>1857.198</v>
+        <v>1876.149</v>
       </c>
       <c r="G100">
         <v>62</v>
@@ -9621,37 +9621,37 @@
         <v>176.225</v>
       </c>
       <c r="M100">
-        <v>437.9272884</v>
+        <v>442.3959342</v>
       </c>
       <c r="N100">
-        <v>-261.7022884</v>
+        <v>-266.1709342</v>
       </c>
       <c r="O100">
-        <v>-53.91067141040001</v>
+        <v>-54.83121244520001</v>
       </c>
       <c r="P100">
-        <v>-207.7916169896</v>
+        <v>-211.3397217548</v>
       </c>
       <c r="Q100">
-        <v>-125.8916169896</v>
+        <v>-129.4397217548</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.459574132431066</v>
+        <v>2.873348264862131</v>
       </c>
       <c r="T100">
-        <v>32.6506728044126</v>
+        <v>65.3013456088252</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08289583901618314</v>
+        <v>0.08205850730894895</v>
       </c>
       <c r="W100">
-        <v>0.216253161159984</v>
+        <v>0.2164506039765499</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.402406985515452</v>
+        <v>0.3983422684900434</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2430195805854057</v>
-      </c>
-      <c r="C101">
-        <v>-1575.944499926088</v>
-      </c>
-      <c r="D101">
-        <v>238.2045000739117</v>
-      </c>
-      <c r="E101">
-        <v>990.1489999999999</v>
-      </c>
-      <c r="F101">
-        <v>1876.149</v>
-      </c>
-      <c r="G101">
-        <v>62</v>
-      </c>
-      <c r="H101">
-        <v>1009.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>258.125</v>
-      </c>
-      <c r="K101">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>176.225</v>
-      </c>
-      <c r="M101">
-        <v>442.3959342</v>
-      </c>
-      <c r="N101">
-        <v>-266.1709342</v>
-      </c>
-      <c r="O101">
-        <v>-54.83121244520001</v>
-      </c>
-      <c r="P101">
-        <v>-211.3397217548</v>
-      </c>
-      <c r="Q101">
-        <v>-129.4397217548</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.873348264862131</v>
-      </c>
-      <c r="T101">
-        <v>65.3013456088252</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08205850730894895</v>
-      </c>
-      <c r="W101">
-        <v>0.2164506039765499</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3983422684900434</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
